--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>126844779</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126844784</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,6 +905,3832 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127303153</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>478581</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6729333</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127303172</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478612</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6729327</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127303371</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>478608</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6729328</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127303322</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>478641</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6729307</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127303609</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80074</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>478556</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6729264</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127303347</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>478585</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6729325</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127302735</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80143</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>478556</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6729264</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127301821</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91339</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>478847</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6729219</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127301869</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>478861</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6729335</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127302772</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>478700</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6729321</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127303012</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>478687</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6729310</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127302578</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80114</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>478547</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6729287</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127303145</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>478716</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6729321</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127303255</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>478825</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6729292</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127303015</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>478546</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6729279</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127303352</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>478560</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6729336</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127302682</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>478682</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6729327</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127303338</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>478615</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6729304</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127303304</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>478650</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6729332</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127302613</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>478547</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6729247</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127303614</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>478567</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6729335</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127301983</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>478888</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6729340</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127301847</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92609</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>478878</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6729286</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127303589</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>478564</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6729339</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127303069</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>478692</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6729327</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127303229</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>478730</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6729317</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På granstubbe.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127302711</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91615</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>658</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>478561</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6729299</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127303130</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>478716</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6729322</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127303112</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>478674</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6729351</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127303176</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91284</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>478757</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6729316</v>
+      </c>
+      <c r="S33" t="n">
+        <v>50</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127303189</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>478644</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6729336</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127303500</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>478575</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6729351</v>
+      </c>
+      <c r="S35" t="n">
+        <v>50</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127303095</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92609</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>478673</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6729316</v>
+      </c>
+      <c r="S36" t="n">
+        <v>50</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127301945</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>478876</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6729339</v>
+      </c>
+      <c r="S37" t="n">
+        <v>50</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127301883</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>478858</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6729321</v>
+      </c>
+      <c r="S38" t="n">
+        <v>50</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127303026</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>478671</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6729323</v>
+      </c>
+      <c r="S39" t="n">
+        <v>50</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127303332</v>
+      </c>
+      <c r="B40" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>478721</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6729322</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126844779</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126844784</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>127303153</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>127303172</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>127303371</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127303322</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303609</v>
+        <v>127303347</v>
       </c>
       <c r="B8" t="n">
-        <v>80074</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478556</v>
+        <v>478585</v>
       </c>
       <c r="R8" t="n">
-        <v>6729264</v>
+        <v>6729325</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,11 +1385,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,44 +1400,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303347</v>
+        <v>127302735</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,17 +1446,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478585</v>
+        <v>478556</v>
       </c>
       <c r="R9" t="n">
-        <v>6729325</v>
+        <v>6729264</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,6 +1486,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,22 +1506,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127302735</v>
+        <v>127303609</v>
       </c>
       <c r="B10" t="n">
-        <v>80143</v>
+        <v>80077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,55 +1624,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127301821</v>
+        <v>127302772</v>
       </c>
       <c r="B11" t="n">
-        <v>91339</v>
+        <v>56849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478847</v>
+        <v>478700</v>
       </c>
       <c r="R11" t="n">
-        <v>6729219</v>
+        <v>6729321</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,35 +1705,39 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127301869</v>
+        <v>127303012</v>
       </c>
       <c r="B12" t="n">
-        <v>79629</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,26 +1745,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1767,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478861</v>
+        <v>478687</v>
       </c>
       <c r="R12" t="n">
-        <v>6729335</v>
+        <v>6729310</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1805,13 +1815,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1830,56 +1844,55 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127302772</v>
+        <v>127301821</v>
       </c>
       <c r="B13" t="n">
-        <v>56849</v>
+        <v>91345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478700</v>
+        <v>478847</v>
       </c>
       <c r="R13" t="n">
-        <v>6729321</v>
+        <v>6729219</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1911,39 +1924,35 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127303012</v>
+        <v>127301869</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,31 +1960,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1983,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478687</v>
+        <v>478861</v>
       </c>
       <c r="R14" t="n">
-        <v>6729310</v>
+        <v>6729335</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2021,17 +2025,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>127302578</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,56 +2156,51 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303145</v>
+        <v>127303015</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478716</v>
+        <v>478546</v>
       </c>
       <c r="R16" t="n">
-        <v>6729321</v>
+        <v>6729279</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,74 +2238,70 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303255</v>
+        <v>127303352</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478825</v>
+        <v>478560</v>
       </c>
       <c r="R17" t="n">
-        <v>6729292</v>
+        <v>6729336</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2348,69 +2339,75 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303015</v>
+        <v>127303145</v>
       </c>
       <c r="B18" t="n">
-        <v>79629</v>
+        <v>56849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478546</v>
+        <v>478716</v>
       </c>
       <c r="R18" t="n">
-        <v>6729279</v>
+        <v>6729321</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2448,70 +2445,74 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303352</v>
+        <v>127303255</v>
       </c>
       <c r="B19" t="n">
-        <v>79629</v>
+        <v>56849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478560</v>
+        <v>478825</v>
       </c>
       <c r="R19" t="n">
-        <v>6729336</v>
+        <v>6729292</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,19 +2550,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
         <v>127302682</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>127303338</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>127303304</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>127302613</v>
       </c>
       <c r="B23" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>127303614</v>
       </c>
       <c r="B24" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3073,10 +3073,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127301983</v>
+        <v>127303589</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478888</v>
+        <v>478564</v>
       </c>
       <c r="R25" t="n">
-        <v>6729340</v>
+        <v>6729339</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3174,32 +3174,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127301847</v>
+        <v>127301983</v>
       </c>
       <c r="B26" t="n">
-        <v>92609</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478878</v>
+        <v>478888</v>
       </c>
       <c r="R26" t="n">
-        <v>6729286</v>
+        <v>6729340</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3248,11 +3248,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3280,32 +3275,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127303589</v>
+        <v>127301847</v>
       </c>
       <c r="B27" t="n">
-        <v>79629</v>
+        <v>92615</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478564</v>
+        <v>478878</v>
       </c>
       <c r="R27" t="n">
-        <v>6729339</v>
+        <v>6729286</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3354,6 +3349,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3384,7 +3384,7 @@
         <v>127303069</v>
       </c>
       <c r="B28" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127303229</v>
+        <v>127302711</v>
       </c>
       <c r="B29" t="n">
-        <v>91544</v>
+        <v>91621</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,26 +3493,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1101</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478730</v>
+        <v>478561</v>
       </c>
       <c r="R29" t="n">
-        <v>6729317</v>
+        <v>6729299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3564,11 +3564,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3591,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127302711</v>
+        <v>127303229</v>
       </c>
       <c r="B30" t="n">
-        <v>91615</v>
+        <v>91550</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,26 +3602,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1101</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3642,10 +3637,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478561</v>
+        <v>478730</v>
       </c>
       <c r="R30" t="n">
-        <v>6729299</v>
+        <v>6729317</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,6 +3673,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3708,7 +3708,7 @@
         <v>127303130</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>127303112</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>127303189</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>127303095</v>
       </c>
       <c r="B36" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>127301945</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127301883</v>
+        <v>127303026</v>
       </c>
       <c r="B38" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478858</v>
+        <v>478671</v>
       </c>
       <c r="R38" t="n">
-        <v>6729321</v>
+        <v>6729323</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4522,51 +4522,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127303026</v>
+        <v>127303332</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>56849</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478671</v>
+        <v>478721</v>
       </c>
       <c r="R39" t="n">
-        <v>6729323</v>
+        <v>6729322</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4598,81 +4603,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127303332</v>
+        <v>127301883</v>
       </c>
       <c r="B40" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478721</v>
+        <v>478858</v>
       </c>
       <c r="R40" t="n">
-        <v>6729322</v>
+        <v>6729321</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4704,29 +4708,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -2050,51 +2050,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302578</v>
+        <v>127303145</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>56849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478547</v>
+        <v>478716</v>
       </c>
       <c r="R15" t="n">
-        <v>6729287</v>
+        <v>6729321</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2126,81 +2131,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303015</v>
+        <v>127303255</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478546</v>
+        <v>478825</v>
       </c>
       <c r="R16" t="n">
-        <v>6729279</v>
+        <v>6729292</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2238,29 +2242,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303352</v>
+        <v>127302578</v>
       </c>
       <c r="B17" t="n">
-        <v>79632</v>
+        <v>80117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478560</v>
+        <v>478547</v>
       </c>
       <c r="R17" t="n">
-        <v>6729336</v>
+        <v>6729287</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2334,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2358,56 +2366,51 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303145</v>
+        <v>127303015</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478716</v>
+        <v>478546</v>
       </c>
       <c r="R18" t="n">
-        <v>6729321</v>
+        <v>6729279</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2445,74 +2448,70 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303255</v>
+        <v>127303352</v>
       </c>
       <c r="B19" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478825</v>
+        <v>478560</v>
       </c>
       <c r="R19" t="n">
-        <v>6729292</v>
+        <v>6729336</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2550,18 +2549,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127302711</v>
+        <v>127303229</v>
       </c>
       <c r="B29" t="n">
-        <v>91621</v>
+        <v>91550</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,26 +3493,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1101</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478561</v>
+        <v>478730</v>
       </c>
       <c r="R29" t="n">
-        <v>6729299</v>
+        <v>6729317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3564,6 +3564,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3591,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127303229</v>
+        <v>127302711</v>
       </c>
       <c r="B30" t="n">
-        <v>91550</v>
+        <v>91621</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3602,26 +3607,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1101</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3637,10 +3642,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478730</v>
+        <v>478561</v>
       </c>
       <c r="R30" t="n">
-        <v>6729317</v>
+        <v>6729299</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3673,11 +3678,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4320,51 +4320,56 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127301945</v>
+        <v>127303332</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478876</v>
+        <v>478721</v>
       </c>
       <c r="R37" t="n">
-        <v>6729339</v>
+        <v>6729322</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4396,35 +4401,39 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127303026</v>
+        <v>127301883</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4432,21 +4441,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4459,10 +4468,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478671</v>
+        <v>478858</v>
       </c>
       <c r="R38" t="n">
-        <v>6729323</v>
+        <v>6729321</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4522,56 +4531,51 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127303332</v>
+        <v>127301945</v>
       </c>
       <c r="B39" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478721</v>
+        <v>478876</v>
       </c>
       <c r="R39" t="n">
-        <v>6729322</v>
+        <v>6729339</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4603,39 +4607,35 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127301883</v>
+        <v>127303026</v>
       </c>
       <c r="B40" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4670,10 +4670,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478858</v>
+        <v>478671</v>
       </c>
       <c r="R40" t="n">
-        <v>6729321</v>
+        <v>6729323</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -2050,56 +2050,51 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127303145</v>
+        <v>127302578</v>
       </c>
       <c r="B15" t="n">
-        <v>56849</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478716</v>
+        <v>478547</v>
       </c>
       <c r="R15" t="n">
-        <v>6729321</v>
+        <v>6729287</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2131,80 +2126,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303255</v>
+        <v>127303015</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478825</v>
+        <v>478546</v>
       </c>
       <c r="R16" t="n">
-        <v>6729292</v>
+        <v>6729279</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2242,28 +2238,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127302578</v>
+        <v>127303352</v>
       </c>
       <c r="B17" t="n">
-        <v>80117</v>
+        <v>79632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,21 +2268,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2298,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478547</v>
+        <v>478560</v>
       </c>
       <c r="R17" t="n">
-        <v>6729287</v>
+        <v>6729336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2334,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,51 +2358,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303015</v>
+        <v>127303145</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478546</v>
+        <v>478716</v>
       </c>
       <c r="R18" t="n">
-        <v>6729279</v>
+        <v>6729321</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2448,70 +2445,74 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303352</v>
+        <v>127303255</v>
       </c>
       <c r="B19" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478560</v>
+        <v>478825</v>
       </c>
       <c r="R19" t="n">
-        <v>6729336</v>
+        <v>6729292</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,19 +2550,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4430,10 +4430,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127301883</v>
+        <v>127301945</v>
       </c>
       <c r="B38" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4441,21 +4441,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478858</v>
+        <v>478876</v>
       </c>
       <c r="R38" t="n">
-        <v>6729321</v>
+        <v>6729339</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4531,7 +4531,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127301945</v>
+        <v>127303026</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478876</v>
+        <v>478671</v>
       </c>
       <c r="R39" t="n">
-        <v>6729339</v>
+        <v>6729323</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4632,10 +4632,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127303026</v>
+        <v>127301883</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4670,10 +4670,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478671</v>
+        <v>478858</v>
       </c>
       <c r="R40" t="n">
-        <v>6729323</v>
+        <v>6729321</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126844779</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126844784</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303347</v>
+        <v>127302735</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478585</v>
+        <v>478556</v>
       </c>
       <c r="R8" t="n">
-        <v>6729325</v>
+        <v>6729264</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,6 +1385,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,44 +1405,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302735</v>
+        <v>127303347</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,17 +1451,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478556</v>
+        <v>478585</v>
       </c>
       <c r="R9" t="n">
-        <v>6729264</v>
+        <v>6729325</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,11 +1491,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,12 +1506,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1624,32 +1624,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127302772</v>
+        <v>127303012</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,17 +1663,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478700</v>
+        <v>478687</v>
       </c>
       <c r="R11" t="n">
-        <v>6729321</v>
+        <v>6729310</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Balningsgrop.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,22 +1722,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303012</v>
+        <v>127301821</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>91346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,31 +1745,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1777,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478687</v>
+        <v>478847</v>
       </c>
       <c r="R12" t="n">
-        <v>6729310</v>
+        <v>6729219</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1815,17 +1814,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1844,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127301821</v>
+        <v>127301869</v>
       </c>
       <c r="B13" t="n">
-        <v>91345</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,28 +1850,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1886,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478847</v>
+        <v>478861</v>
       </c>
       <c r="R13" t="n">
-        <v>6729219</v>
+        <v>6729335</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1949,51 +1940,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127301869</v>
+        <v>127302772</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478861</v>
+        <v>478700</v>
       </c>
       <c r="R14" t="n">
-        <v>6729335</v>
+        <v>6729321</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2025,25 +2021,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127303304</v>
+        <v>127302613</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,21 +2781,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2804,17 +2804,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478650</v>
+        <v>478547</v>
       </c>
       <c r="R22" t="n">
-        <v>6729332</v>
+        <v>6729247</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2859,19 +2859,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302613</v>
+        <v>127303614</v>
       </c>
       <c r="B23" t="n">
         <v>78773</v>
@@ -2905,17 +2905,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478547</v>
+        <v>478567</v>
       </c>
       <c r="R23" t="n">
-        <v>6729247</v>
+        <v>6729335</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2960,22 +2960,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127303614</v>
+        <v>127303304</v>
       </c>
       <c r="B24" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,21 +2983,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478567</v>
+        <v>478650</v>
       </c>
       <c r="R24" t="n">
-        <v>6729335</v>
+        <v>6729332</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3278,7 +3278,7 @@
         <v>127301847</v>
       </c>
       <c r="B27" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127303229</v>
+        <v>127302711</v>
       </c>
       <c r="B29" t="n">
-        <v>91550</v>
+        <v>91622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,26 +3493,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1101</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478730</v>
+        <v>478561</v>
       </c>
       <c r="R29" t="n">
-        <v>6729317</v>
+        <v>6729299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3564,11 +3564,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3591,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127302711</v>
+        <v>127303229</v>
       </c>
       <c r="B30" t="n">
-        <v>91621</v>
+        <v>91551</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,26 +3602,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1101</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3642,10 +3637,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478561</v>
+        <v>478730</v>
       </c>
       <c r="R30" t="n">
-        <v>6729299</v>
+        <v>6729317</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,6 +3673,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3910,7 +3910,7 @@
         <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>127303095</v>
       </c>
       <c r="B36" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4320,56 +4320,51 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127303332</v>
+        <v>127301945</v>
       </c>
       <c r="B37" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478721</v>
+        <v>478876</v>
       </c>
       <c r="R37" t="n">
-        <v>6729322</v>
+        <v>6729339</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4401,36 +4396,32 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127301945</v>
+        <v>127303026</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4468,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478876</v>
+        <v>478671</v>
       </c>
       <c r="R38" t="n">
-        <v>6729339</v>
+        <v>6729323</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4531,51 +4522,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127303026</v>
+        <v>127303332</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478671</v>
+        <v>478721</v>
       </c>
       <c r="R39" t="n">
-        <v>6729323</v>
+        <v>6729322</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4607,25 +4603,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127302735</v>
+        <v>127303347</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478556</v>
+        <v>478585</v>
       </c>
       <c r="R8" t="n">
-        <v>6729264</v>
+        <v>6729325</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,11 +1385,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,44 +1400,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303347</v>
+        <v>127302735</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,17 +1446,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478585</v>
+        <v>478556</v>
       </c>
       <c r="R9" t="n">
-        <v>6729325</v>
+        <v>6729264</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,6 +1486,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,12 +1506,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303012</v>
+        <v>127301821</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>91346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,31 +1635,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1667,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478687</v>
+        <v>478847</v>
       </c>
       <c r="R11" t="n">
-        <v>6729310</v>
+        <v>6729219</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1705,17 +1704,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1734,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127301821</v>
+        <v>127301869</v>
       </c>
       <c r="B12" t="n">
-        <v>91346</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,28 +1740,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1776,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478847</v>
+        <v>478861</v>
       </c>
       <c r="R12" t="n">
-        <v>6729219</v>
+        <v>6729335</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1839,51 +1830,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127301869</v>
+        <v>127302772</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478861</v>
+        <v>478700</v>
       </c>
       <c r="R13" t="n">
-        <v>6729335</v>
+        <v>6729321</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1915,57 +1911,61 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127302772</v>
+        <v>127303012</v>
       </c>
       <c r="B14" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,17 +1979,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478700</v>
+        <v>478687</v>
       </c>
       <c r="R14" t="n">
-        <v>6729321</v>
+        <v>6729310</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Balningsgrop.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,63 +2038,68 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302578</v>
+        <v>127303145</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>56849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478547</v>
+        <v>478716</v>
       </c>
       <c r="R15" t="n">
-        <v>6729287</v>
+        <v>6729321</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2126,81 +2131,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303015</v>
+        <v>127303255</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478546</v>
+        <v>478825</v>
       </c>
       <c r="R16" t="n">
-        <v>6729279</v>
+        <v>6729292</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2238,29 +2242,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303352</v>
+        <v>127302578</v>
       </c>
       <c r="B17" t="n">
-        <v>79632</v>
+        <v>80117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478560</v>
+        <v>478547</v>
       </c>
       <c r="R17" t="n">
-        <v>6729336</v>
+        <v>6729287</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2334,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2358,56 +2366,51 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303145</v>
+        <v>127303015</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478716</v>
+        <v>478546</v>
       </c>
       <c r="R18" t="n">
-        <v>6729321</v>
+        <v>6729279</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2445,74 +2448,70 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303255</v>
+        <v>127303352</v>
       </c>
       <c r="B19" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478825</v>
+        <v>478560</v>
       </c>
       <c r="R19" t="n">
-        <v>6729292</v>
+        <v>6729336</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2550,18 +2549,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127302613</v>
+        <v>127303304</v>
       </c>
       <c r="B22" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,21 +2781,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2804,17 +2804,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478547</v>
+        <v>478650</v>
       </c>
       <c r="R22" t="n">
-        <v>6729247</v>
+        <v>6729332</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2859,19 +2859,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127303614</v>
+        <v>127302613</v>
       </c>
       <c r="B23" t="n">
         <v>78773</v>
@@ -2905,17 +2905,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478567</v>
+        <v>478547</v>
       </c>
       <c r="R23" t="n">
-        <v>6729335</v>
+        <v>6729247</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2960,22 +2960,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127303304</v>
+        <v>127303614</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,21 +2983,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478650</v>
+        <v>478567</v>
       </c>
       <c r="R24" t="n">
-        <v>6729332</v>
+        <v>6729335</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127303153</v>
+        <v>127303172</v>
       </c>
       <c r="B4" t="n">
         <v>79014</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478581</v>
+        <v>478612</v>
       </c>
       <c r="R4" t="n">
-        <v>6729333</v>
+        <v>6729327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127303172</v>
+        <v>127303153</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478612</v>
+        <v>478581</v>
       </c>
       <c r="R5" t="n">
-        <v>6729327</v>
+        <v>6729333</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1830,32 +1830,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127302772</v>
+        <v>127303012</v>
       </c>
       <c r="B13" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1869,17 +1869,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478700</v>
+        <v>478687</v>
       </c>
       <c r="R13" t="n">
-        <v>6729321</v>
+        <v>6729310</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Balningsgrop.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,44 +1928,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127303012</v>
+        <v>127302772</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,17 +1979,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478687</v>
+        <v>478700</v>
       </c>
       <c r="R14" t="n">
-        <v>6729310</v>
+        <v>6729321</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Balningsgrop.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,68 +2038,63 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127303145</v>
+        <v>127303015</v>
       </c>
       <c r="B15" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478716</v>
+        <v>478546</v>
       </c>
       <c r="R15" t="n">
-        <v>6729321</v>
+        <v>6729279</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2137,74 +2132,70 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303255</v>
+        <v>127303352</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478825</v>
+        <v>478560</v>
       </c>
       <c r="R16" t="n">
-        <v>6729292</v>
+        <v>6729336</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2242,69 +2233,75 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127302578</v>
+        <v>127303145</v>
       </c>
       <c r="B17" t="n">
-        <v>80117</v>
+        <v>56849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478547</v>
+        <v>478716</v>
       </c>
       <c r="R17" t="n">
-        <v>6729287</v>
+        <v>6729321</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2336,81 +2333,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303015</v>
+        <v>127303255</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478546</v>
+        <v>478825</v>
       </c>
       <c r="R18" t="n">
-        <v>6729279</v>
+        <v>6729292</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2448,29 +2444,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303352</v>
+        <v>127302578</v>
       </c>
       <c r="B19" t="n">
-        <v>79632</v>
+        <v>80117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,21 +2473,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2505,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478560</v>
+        <v>478547</v>
       </c>
       <c r="R19" t="n">
-        <v>6729336</v>
+        <v>6729287</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,6 +2536,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3073,32 +3073,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127303589</v>
+        <v>127301847</v>
       </c>
       <c r="B25" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478564</v>
+        <v>478878</v>
       </c>
       <c r="R25" t="n">
-        <v>6729339</v>
+        <v>6729286</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3147,6 +3147,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3174,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127301983</v>
+        <v>127303589</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3185,21 +3190,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3212,10 +3217,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478888</v>
+        <v>478564</v>
       </c>
       <c r="R26" t="n">
-        <v>6729340</v>
+        <v>6729339</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3275,32 +3280,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127301847</v>
+        <v>127301983</v>
       </c>
       <c r="B27" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478878</v>
+        <v>478888</v>
       </c>
       <c r="R27" t="n">
-        <v>6729286</v>
+        <v>6729340</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3349,11 +3354,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127303371</v>
+        <v>127303322</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478608</v>
+        <v>478641</v>
       </c>
       <c r="R6" t="n">
-        <v>6729328</v>
+        <v>6729307</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127303322</v>
+        <v>127303371</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478641</v>
+        <v>478608</v>
       </c>
       <c r="R7" t="n">
-        <v>6729307</v>
+        <v>6729328</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303347</v>
+        <v>127303609</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>80077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478585</v>
+        <v>478556</v>
       </c>
       <c r="R8" t="n">
-        <v>6729325</v>
+        <v>6729264</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,6 +1385,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,44 +1405,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302735</v>
+        <v>127303347</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,17 +1451,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478556</v>
+        <v>478585</v>
       </c>
       <c r="R9" t="n">
-        <v>6729264</v>
+        <v>6729325</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,11 +1491,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,22 +1506,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127303609</v>
+        <v>127302735</v>
       </c>
       <c r="B10" t="n">
-        <v>80077</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,55 +1624,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127301821</v>
+        <v>127302772</v>
       </c>
       <c r="B11" t="n">
-        <v>91346</v>
+        <v>56849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478847</v>
+        <v>478700</v>
       </c>
       <c r="R11" t="n">
-        <v>6729219</v>
+        <v>6729321</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,35 +1705,39 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127301869</v>
+        <v>127301821</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>91346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,24 +1745,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1767,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478861</v>
+        <v>478847</v>
       </c>
       <c r="R12" t="n">
-        <v>6729335</v>
+        <v>6729219</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1830,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127303012</v>
+        <v>127301869</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,31 +1850,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1873,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478687</v>
+        <v>478861</v>
       </c>
       <c r="R13" t="n">
-        <v>6729310</v>
+        <v>6729335</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1911,17 +1915,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127302772</v>
+        <v>127303012</v>
       </c>
       <c r="B14" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,17 +1979,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478700</v>
+        <v>478687</v>
       </c>
       <c r="R14" t="n">
-        <v>6729321</v>
+        <v>6729310</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Balningsgrop.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,12 +2038,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303130</v>
+        <v>127303112</v>
       </c>
       <c r="B31" t="n">
         <v>79014</v>
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478716</v>
+        <v>478674</v>
       </c>
       <c r="R31" t="n">
-        <v>6729322</v>
+        <v>6729351</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,32 +3806,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303112</v>
+        <v>127303176</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3840,17 +3840,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478674</v>
+        <v>478757</v>
       </c>
       <c r="R32" t="n">
-        <v>6729351</v>
+        <v>6729316</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3895,44 +3895,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303176</v>
+        <v>127303130</v>
       </c>
       <c r="B33" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478757</v>
+        <v>478716</v>
       </c>
       <c r="R33" t="n">
-        <v>6729316</v>
+        <v>6729322</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303609</v>
+        <v>127303347</v>
       </c>
       <c r="B8" t="n">
-        <v>80077</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478556</v>
+        <v>478585</v>
       </c>
       <c r="R8" t="n">
-        <v>6729264</v>
+        <v>6729325</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,11 +1385,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,44 +1400,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303347</v>
+        <v>127302735</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,17 +1446,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478585</v>
+        <v>478556</v>
       </c>
       <c r="R9" t="n">
-        <v>6729325</v>
+        <v>6729264</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,6 +1486,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,22 +1506,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127302735</v>
+        <v>127303609</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>80077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3705,7 +3705,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303112</v>
+        <v>127303130</v>
       </c>
       <c r="B31" t="n">
         <v>79014</v>
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478674</v>
+        <v>478716</v>
       </c>
       <c r="R31" t="n">
-        <v>6729351</v>
+        <v>6729322</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,32 +3806,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303176</v>
+        <v>127303112</v>
       </c>
       <c r="B32" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3840,17 +3840,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478757</v>
+        <v>478674</v>
       </c>
       <c r="R32" t="n">
-        <v>6729316</v>
+        <v>6729351</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3895,44 +3895,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303130</v>
+        <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478716</v>
+        <v>478757</v>
       </c>
       <c r="R33" t="n">
-        <v>6729322</v>
+        <v>6729316</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4522,56 +4522,51 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127303332</v>
+        <v>127301883</v>
       </c>
       <c r="B39" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478721</v>
+        <v>478858</v>
       </c>
       <c r="R39" t="n">
-        <v>6729322</v>
+        <v>6729321</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4603,80 +4598,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127301883</v>
+        <v>127303332</v>
       </c>
       <c r="B40" t="n">
-        <v>78773</v>
+        <v>56849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478858</v>
+        <v>478721</v>
       </c>
       <c r="R40" t="n">
-        <v>6729321</v>
+        <v>6729322</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4708,25 +4704,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126844779</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126844784</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127303172</v>
+        <v>127303153</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478612</v>
+        <v>478581</v>
       </c>
       <c r="R4" t="n">
-        <v>6729327</v>
+        <v>6729333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127303153</v>
+        <v>127303172</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478581</v>
+        <v>478612</v>
       </c>
       <c r="R5" t="n">
-        <v>6729333</v>
+        <v>6729327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127303322</v>
+        <v>127303371</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478641</v>
+        <v>478608</v>
       </c>
       <c r="R6" t="n">
-        <v>6729307</v>
+        <v>6729328</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127303371</v>
+        <v>127303322</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478608</v>
+        <v>478641</v>
       </c>
       <c r="R7" t="n">
-        <v>6729328</v>
+        <v>6729307</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1314,7 +1314,7 @@
         <v>127303347</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127302735</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>127303609</v>
       </c>
       <c r="B10" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,56 +1624,55 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127302772</v>
+        <v>127301821</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478700</v>
+        <v>478847</v>
       </c>
       <c r="R11" t="n">
-        <v>6729321</v>
+        <v>6729219</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,39 +1704,35 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127301821</v>
+        <v>127301869</v>
       </c>
       <c r="B12" t="n">
-        <v>91346</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,28 +1740,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1776,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478847</v>
+        <v>478861</v>
       </c>
       <c r="R12" t="n">
-        <v>6729219</v>
+        <v>6729335</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1839,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127301869</v>
+        <v>127303012</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,26 +1841,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1877,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478861</v>
+        <v>478687</v>
       </c>
       <c r="R13" t="n">
-        <v>6729335</v>
+        <v>6729310</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1915,13 +1911,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127303012</v>
+        <v>127302772</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>56853</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,17 +1979,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478687</v>
+        <v>478700</v>
       </c>
       <c r="R14" t="n">
-        <v>6729310</v>
+        <v>6729321</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Balningsgrop.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,12 +2038,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2053,7 +2053,7 @@
         <v>127303015</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>127303352</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,56 +2252,51 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303145</v>
+        <v>127302578</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>80121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478716</v>
+        <v>478547</v>
       </c>
       <c r="R17" t="n">
-        <v>6729321</v>
+        <v>6729287</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2333,34 +2328,40 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303255</v>
+        <v>127303145</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2391,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2400,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478825</v>
+        <v>478716</v>
       </c>
       <c r="R18" t="n">
-        <v>6729292</v>
+        <v>6729321</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2462,51 +2463,56 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127302578</v>
+        <v>127303255</v>
       </c>
       <c r="B19" t="n">
-        <v>80117</v>
+        <v>56853</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478547</v>
+        <v>478825</v>
       </c>
       <c r="R19" t="n">
-        <v>6729287</v>
+        <v>6729292</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,30 +2544,24 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
         <v>127302682</v>
       </c>
       <c r="B20" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>127303338</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127303304</v>
+        <v>127302613</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,21 +2781,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2804,17 +2804,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478650</v>
+        <v>478547</v>
       </c>
       <c r="R22" t="n">
-        <v>6729332</v>
+        <v>6729247</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2859,22 +2859,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302613</v>
+        <v>127303614</v>
       </c>
       <c r="B23" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,17 +2905,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478547</v>
+        <v>478567</v>
       </c>
       <c r="R23" t="n">
-        <v>6729247</v>
+        <v>6729335</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2960,22 +2960,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127303614</v>
+        <v>127303304</v>
       </c>
       <c r="B24" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,21 +2983,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478567</v>
+        <v>478650</v>
       </c>
       <c r="R24" t="n">
-        <v>6729335</v>
+        <v>6729332</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3073,32 +3073,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127301847</v>
+        <v>127303589</v>
       </c>
       <c r="B25" t="n">
-        <v>92616</v>
+        <v>79636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478878</v>
+        <v>478564</v>
       </c>
       <c r="R25" t="n">
-        <v>6729286</v>
+        <v>6729339</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3147,11 +3147,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3179,10 +3174,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127303589</v>
+        <v>127301983</v>
       </c>
       <c r="B26" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,21 +3185,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3217,10 +3212,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478564</v>
+        <v>478888</v>
       </c>
       <c r="R26" t="n">
-        <v>6729339</v>
+        <v>6729340</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3280,32 +3275,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127301983</v>
+        <v>127301847</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478888</v>
+        <v>478878</v>
       </c>
       <c r="R27" t="n">
-        <v>6729340</v>
+        <v>6729286</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3354,6 +3349,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3384,7 +3384,7 @@
         <v>127303069</v>
       </c>
       <c r="B28" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127302711</v>
+        <v>127303229</v>
       </c>
       <c r="B29" t="n">
-        <v>91622</v>
+        <v>91555</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,26 +3493,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1101</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478561</v>
+        <v>478730</v>
       </c>
       <c r="R29" t="n">
-        <v>6729299</v>
+        <v>6729317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3564,6 +3564,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3591,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127303229</v>
+        <v>127302711</v>
       </c>
       <c r="B30" t="n">
-        <v>91551</v>
+        <v>91626</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3602,26 +3607,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1101</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3637,10 +3642,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478730</v>
+        <v>478561</v>
       </c>
       <c r="R30" t="n">
-        <v>6729317</v>
+        <v>6729299</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3673,11 +3678,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3708,7 +3708,7 @@
         <v>127303130</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>127303112</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>127303189</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>127303500</v>
       </c>
       <c r="B35" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>127303095</v>
       </c>
       <c r="B36" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4320,10 +4320,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127301945</v>
+        <v>127301883</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4331,21 +4331,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478876</v>
+        <v>478858</v>
       </c>
       <c r="R37" t="n">
-        <v>6729339</v>
+        <v>6729321</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127303026</v>
+        <v>127301945</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478671</v>
+        <v>478876</v>
       </c>
       <c r="R38" t="n">
-        <v>6729323</v>
+        <v>6729339</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4522,10 +4522,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127301883</v>
+        <v>127303026</v>
       </c>
       <c r="B39" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4533,21 +4533,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478858</v>
+        <v>478671</v>
       </c>
       <c r="R39" t="n">
-        <v>6729321</v>
+        <v>6729323</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4626,7 +4626,7 @@
         <v>127303332</v>
       </c>
       <c r="B40" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127303015</v>
+        <v>127302578</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478546</v>
+        <v>478547</v>
       </c>
       <c r="R15" t="n">
-        <v>6729279</v>
+        <v>6729287</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,6 +2124,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,7 +2156,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303352</v>
+        <v>127303015</v>
       </c>
       <c r="B16" t="n">
         <v>79636</v>
@@ -2189,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478560</v>
+        <v>478546</v>
       </c>
       <c r="R16" t="n">
-        <v>6729336</v>
+        <v>6729279</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,10 +2257,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127302578</v>
+        <v>127303352</v>
       </c>
       <c r="B17" t="n">
-        <v>80121</v>
+        <v>79636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2263,21 +2268,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478547</v>
+        <v>478560</v>
       </c>
       <c r="R17" t="n">
-        <v>6729287</v>
+        <v>6729336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2770,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127302613</v>
+        <v>127303304</v>
       </c>
       <c r="B22" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,21 +2781,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2804,17 +2804,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478547</v>
+        <v>478650</v>
       </c>
       <c r="R22" t="n">
-        <v>6729247</v>
+        <v>6729332</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2859,19 +2859,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127303614</v>
+        <v>127302613</v>
       </c>
       <c r="B23" t="n">
         <v>78777</v>
@@ -2905,17 +2905,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478567</v>
+        <v>478547</v>
       </c>
       <c r="R23" t="n">
-        <v>6729335</v>
+        <v>6729247</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2960,22 +2960,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127303304</v>
+        <v>127303614</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,21 +2983,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478650</v>
+        <v>478567</v>
       </c>
       <c r="R24" t="n">
-        <v>6729332</v>
+        <v>6729335</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303130</v>
+        <v>127303176</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,17 +3739,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478716</v>
+        <v>478757</v>
       </c>
       <c r="R31" t="n">
-        <v>6729322</v>
+        <v>6729316</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3794,19 +3794,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303112</v>
+        <v>127303130</v>
       </c>
       <c r="B32" t="n">
         <v>79018</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478674</v>
+        <v>478716</v>
       </c>
       <c r="R32" t="n">
-        <v>6729351</v>
+        <v>6729322</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303176</v>
+        <v>127303112</v>
       </c>
       <c r="B33" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478757</v>
+        <v>478674</v>
       </c>
       <c r="R33" t="n">
-        <v>6729316</v>
+        <v>6729351</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127301883</v>
+        <v>127301945</v>
       </c>
       <c r="B37" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4331,21 +4331,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478858</v>
+        <v>478876</v>
       </c>
       <c r="R37" t="n">
-        <v>6729321</v>
+        <v>6729339</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127301945</v>
+        <v>127303026</v>
       </c>
       <c r="B38" t="n">
         <v>79018</v>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478876</v>
+        <v>478671</v>
       </c>
       <c r="R38" t="n">
-        <v>6729339</v>
+        <v>6729323</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4522,51 +4522,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127303026</v>
+        <v>127303332</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478671</v>
+        <v>478721</v>
       </c>
       <c r="R39" t="n">
-        <v>6729323</v>
+        <v>6729322</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4598,81 +4603,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127303332</v>
+        <v>127301883</v>
       </c>
       <c r="B40" t="n">
-        <v>56853</v>
+        <v>78777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478721</v>
+        <v>478858</v>
       </c>
       <c r="R40" t="n">
-        <v>6729322</v>
+        <v>6729321</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4704,29 +4708,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303347</v>
+        <v>127303609</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>80081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478585</v>
+        <v>478556</v>
       </c>
       <c r="R8" t="n">
-        <v>6729325</v>
+        <v>6729264</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,6 +1385,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,44 +1405,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302735</v>
+        <v>127303347</v>
       </c>
       <c r="B9" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,17 +1451,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478556</v>
+        <v>478585</v>
       </c>
       <c r="R9" t="n">
-        <v>6729264</v>
+        <v>6729325</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,11 +1491,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,22 +1506,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127303609</v>
+        <v>127302735</v>
       </c>
       <c r="B10" t="n">
-        <v>80081</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127301821</v>
+        <v>127301869</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,28 +1635,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478847</v>
+        <v>478861</v>
       </c>
       <c r="R11" t="n">
-        <v>6729219</v>
+        <v>6729335</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1729,51 +1725,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127301869</v>
+        <v>127302772</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>56853</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478861</v>
+        <v>478700</v>
       </c>
       <c r="R12" t="n">
-        <v>6729335</v>
+        <v>6729321</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1805,25 +1806,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1940,56 +1945,55 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127302772</v>
+        <v>127301821</v>
       </c>
       <c r="B14" t="n">
-        <v>56853</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478700</v>
+        <v>478847</v>
       </c>
       <c r="R14" t="n">
-        <v>6729321</v>
+        <v>6729219</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,29 +2025,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3073,32 +3073,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127303589</v>
+        <v>127301847</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478564</v>
+        <v>478878</v>
       </c>
       <c r="R25" t="n">
-        <v>6729339</v>
+        <v>6729286</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3147,6 +3147,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3174,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127301983</v>
+        <v>127303589</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3185,21 +3190,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3212,10 +3217,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478888</v>
+        <v>478564</v>
       </c>
       <c r="R26" t="n">
-        <v>6729340</v>
+        <v>6729339</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3275,32 +3280,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127301847</v>
+        <v>127301983</v>
       </c>
       <c r="B27" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478878</v>
+        <v>478888</v>
       </c>
       <c r="R27" t="n">
-        <v>6729286</v>
+        <v>6729340</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3349,11 +3354,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3705,32 +3705,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303176</v>
+        <v>127303130</v>
       </c>
       <c r="B31" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,17 +3739,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478757</v>
+        <v>478716</v>
       </c>
       <c r="R31" t="n">
-        <v>6729316</v>
+        <v>6729322</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3794,19 +3794,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303130</v>
+        <v>127303112</v>
       </c>
       <c r="B32" t="n">
         <v>79018</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478716</v>
+        <v>478674</v>
       </c>
       <c r="R32" t="n">
-        <v>6729322</v>
+        <v>6729351</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303112</v>
+        <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478674</v>
+        <v>478757</v>
       </c>
       <c r="R33" t="n">
-        <v>6729351</v>
+        <v>6729316</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127301869</v>
+        <v>127301821</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,24 +1635,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1662,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478861</v>
+        <v>478847</v>
       </c>
       <c r="R11" t="n">
-        <v>6729335</v>
+        <v>6729219</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1725,56 +1729,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127302772</v>
+        <v>127301869</v>
       </c>
       <c r="B12" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478700</v>
+        <v>478861</v>
       </c>
       <c r="R12" t="n">
-        <v>6729321</v>
+        <v>6729335</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,29 +1805,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1945,55 +1940,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127301821</v>
+        <v>127302772</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>56853</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478847</v>
+        <v>478700</v>
       </c>
       <c r="R14" t="n">
-        <v>6729219</v>
+        <v>6729321</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2025,76 +2021,85 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302578</v>
+        <v>127303145</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>56853</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478547</v>
+        <v>478716</v>
       </c>
       <c r="R15" t="n">
-        <v>6729287</v>
+        <v>6729321</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2126,81 +2131,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303015</v>
+        <v>127303255</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>56853</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478546</v>
+        <v>478825</v>
       </c>
       <c r="R16" t="n">
-        <v>6729279</v>
+        <v>6729292</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2238,29 +2242,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303352</v>
+        <v>127302578</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>80121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478560</v>
+        <v>478547</v>
       </c>
       <c r="R17" t="n">
-        <v>6729336</v>
+        <v>6729287</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2334,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2358,56 +2366,51 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303145</v>
+        <v>127303015</v>
       </c>
       <c r="B18" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478716</v>
+        <v>478546</v>
       </c>
       <c r="R18" t="n">
-        <v>6729321</v>
+        <v>6729279</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2445,74 +2448,70 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303255</v>
+        <v>127303352</v>
       </c>
       <c r="B19" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478825</v>
+        <v>478560</v>
       </c>
       <c r="R19" t="n">
-        <v>6729292</v>
+        <v>6729336</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2550,18 +2549,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303130</v>
+        <v>127303176</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,17 +3739,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478716</v>
+        <v>478757</v>
       </c>
       <c r="R31" t="n">
-        <v>6729322</v>
+        <v>6729316</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3794,19 +3794,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303112</v>
+        <v>127303130</v>
       </c>
       <c r="B32" t="n">
         <v>79018</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478674</v>
+        <v>478716</v>
       </c>
       <c r="R32" t="n">
-        <v>6729351</v>
+        <v>6729322</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303176</v>
+        <v>127303112</v>
       </c>
       <c r="B33" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478757</v>
+        <v>478674</v>
       </c>
       <c r="R33" t="n">
-        <v>6729316</v>
+        <v>6729351</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126844779</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126844784</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303609</v>
+        <v>127303347</v>
       </c>
       <c r="B8" t="n">
-        <v>80081</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478556</v>
+        <v>478585</v>
       </c>
       <c r="R8" t="n">
-        <v>6729264</v>
+        <v>6729325</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,11 +1385,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,44 +1400,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303347</v>
+        <v>127302735</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,17 +1446,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478585</v>
+        <v>478556</v>
       </c>
       <c r="R9" t="n">
-        <v>6729325</v>
+        <v>6729264</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,6 +1486,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,22 +1506,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127302735</v>
+        <v>127303609</v>
       </c>
       <c r="B10" t="n">
-        <v>80150</v>
+        <v>80081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127301821</v>
+        <v>127301869</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,28 +1635,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478847</v>
+        <v>478861</v>
       </c>
       <c r="R11" t="n">
-        <v>6729219</v>
+        <v>6729335</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1729,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127301869</v>
+        <v>127301821</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,24 +1736,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478861</v>
+        <v>478847</v>
       </c>
       <c r="R12" t="n">
-        <v>6729335</v>
+        <v>6729219</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -3073,32 +3073,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127301847</v>
+        <v>127301983</v>
       </c>
       <c r="B25" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478878</v>
+        <v>478888</v>
       </c>
       <c r="R25" t="n">
-        <v>6729286</v>
+        <v>6729340</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3147,11 +3147,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3179,32 +3174,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127303589</v>
+        <v>127301847</v>
       </c>
       <c r="B26" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3217,10 +3212,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478564</v>
+        <v>478878</v>
       </c>
       <c r="R26" t="n">
-        <v>6729339</v>
+        <v>6729286</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3253,6 +3248,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127301983</v>
+        <v>127303589</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,21 +3291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478888</v>
+        <v>478564</v>
       </c>
       <c r="R27" t="n">
-        <v>6729340</v>
+        <v>6729339</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127303229</v>
+        <v>127302711</v>
       </c>
       <c r="B29" t="n">
-        <v>91555</v>
+        <v>91626</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,26 +3493,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1101</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478730</v>
+        <v>478561</v>
       </c>
       <c r="R29" t="n">
-        <v>6729317</v>
+        <v>6729299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3564,11 +3564,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3591,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127302711</v>
+        <v>127303229</v>
       </c>
       <c r="B30" t="n">
-        <v>91626</v>
+        <v>91555</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,26 +3602,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1101</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3642,10 +3637,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478561</v>
+        <v>478730</v>
       </c>
       <c r="R30" t="n">
-        <v>6729299</v>
+        <v>6729317</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,6 +3673,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3705,32 +3705,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303176</v>
+        <v>127303130</v>
       </c>
       <c r="B31" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,17 +3739,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478757</v>
+        <v>478716</v>
       </c>
       <c r="R31" t="n">
-        <v>6729316</v>
+        <v>6729322</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3794,19 +3794,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303130</v>
+        <v>127303112</v>
       </c>
       <c r="B32" t="n">
         <v>79018</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478716</v>
+        <v>478674</v>
       </c>
       <c r="R32" t="n">
-        <v>6729322</v>
+        <v>6729351</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303112</v>
+        <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478674</v>
+        <v>478757</v>
       </c>
       <c r="R33" t="n">
-        <v>6729351</v>
+        <v>6729316</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -3174,32 +3174,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127301847</v>
+        <v>127303589</v>
       </c>
       <c r="B26" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478878</v>
+        <v>478564</v>
       </c>
       <c r="R26" t="n">
-        <v>6729286</v>
+        <v>6729339</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3248,11 +3248,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3280,32 +3275,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127303589</v>
+        <v>127301847</v>
       </c>
       <c r="B27" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478564</v>
+        <v>478878</v>
       </c>
       <c r="R27" t="n">
-        <v>6729339</v>
+        <v>6729286</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3354,6 +3349,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>127303153</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>127303172</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>127303371</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127303322</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127303347</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127302735</v>
       </c>
       <c r="B9" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>127303609</v>
       </c>
       <c r="B10" t="n">
-        <v>80081</v>
+        <v>80083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127301869</v>
+        <v>127301821</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>91352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,24 +1635,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1662,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478861</v>
+        <v>478847</v>
       </c>
       <c r="R11" t="n">
-        <v>6729335</v>
+        <v>6729219</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1725,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127301821</v>
+        <v>127301869</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>79638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,28 +1740,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478847</v>
+        <v>478861</v>
       </c>
       <c r="R12" t="n">
-        <v>6729219</v>
+        <v>6729335</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1830,32 +1830,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127303012</v>
+        <v>127302772</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>56855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1869,17 +1869,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478687</v>
+        <v>478700</v>
       </c>
       <c r="R13" t="n">
-        <v>6729310</v>
+        <v>6729321</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Balningsgrop.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,44 +1928,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127302772</v>
+        <v>127303012</v>
       </c>
       <c r="B14" t="n">
-        <v>56853</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,17 +1979,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478700</v>
+        <v>478687</v>
       </c>
       <c r="R14" t="n">
-        <v>6729321</v>
+        <v>6729310</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Balningsgrop.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,68 +2038,63 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127303145</v>
+        <v>127302578</v>
       </c>
       <c r="B15" t="n">
-        <v>56853</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478716</v>
+        <v>478547</v>
       </c>
       <c r="R15" t="n">
-        <v>6729321</v>
+        <v>6729287</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2131,80 +2126,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303255</v>
+        <v>127303015</v>
       </c>
       <c r="B16" t="n">
-        <v>56853</v>
+        <v>79638</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478825</v>
+        <v>478546</v>
       </c>
       <c r="R16" t="n">
-        <v>6729292</v>
+        <v>6729279</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2242,28 +2238,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127302578</v>
+        <v>127303352</v>
       </c>
       <c r="B17" t="n">
-        <v>80121</v>
+        <v>79638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,21 +2268,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2298,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478547</v>
+        <v>478560</v>
       </c>
       <c r="R17" t="n">
-        <v>6729287</v>
+        <v>6729336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2334,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,51 +2358,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303015</v>
+        <v>127303145</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>56855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478546</v>
+        <v>478716</v>
       </c>
       <c r="R18" t="n">
-        <v>6729279</v>
+        <v>6729321</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2448,70 +2445,74 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303352</v>
+        <v>127303255</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>56855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478560</v>
+        <v>478825</v>
       </c>
       <c r="R19" t="n">
-        <v>6729336</v>
+        <v>6729292</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,19 +2550,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
         <v>127302682</v>
       </c>
       <c r="B20" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>127303338</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>127303304</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>127302613</v>
       </c>
       <c r="B23" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>127303614</v>
       </c>
       <c r="B24" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3073,10 +3073,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127301983</v>
+        <v>127303589</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478888</v>
+        <v>478564</v>
       </c>
       <c r="R25" t="n">
-        <v>6729340</v>
+        <v>6729339</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127303589</v>
+        <v>127301983</v>
       </c>
       <c r="B26" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478564</v>
+        <v>478888</v>
       </c>
       <c r="R26" t="n">
-        <v>6729339</v>
+        <v>6729340</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3278,7 +3278,7 @@
         <v>127301847</v>
       </c>
       <c r="B27" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>127303069</v>
       </c>
       <c r="B28" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>127302711</v>
       </c>
       <c r="B29" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>127303229</v>
       </c>
       <c r="B30" t="n">
-        <v>91555</v>
+        <v>91557</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>127303130</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>127303112</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>127303189</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>127303500</v>
       </c>
       <c r="B35" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>127303095</v>
       </c>
       <c r="B36" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4320,10 +4320,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127301945</v>
+        <v>127303026</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478876</v>
+        <v>478671</v>
       </c>
       <c r="R37" t="n">
-        <v>6729339</v>
+        <v>6729323</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127303026</v>
+        <v>127301883</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478671</v>
+        <v>478858</v>
       </c>
       <c r="R38" t="n">
-        <v>6729323</v>
+        <v>6729321</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4522,56 +4522,51 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127303332</v>
+        <v>127301945</v>
       </c>
       <c r="B39" t="n">
-        <v>56853</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478721</v>
+        <v>478876</v>
       </c>
       <c r="R39" t="n">
-        <v>6729322</v>
+        <v>6729339</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4603,80 +4598,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127301883</v>
+        <v>127303332</v>
       </c>
       <c r="B40" t="n">
-        <v>78777</v>
+        <v>56855</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478858</v>
+        <v>478721</v>
       </c>
       <c r="R40" t="n">
-        <v>6729321</v>
+        <v>6729322</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4708,25 +4704,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1830,32 +1830,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127302772</v>
+        <v>127303012</v>
       </c>
       <c r="B13" t="n">
-        <v>56855</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1869,17 +1869,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478700</v>
+        <v>478687</v>
       </c>
       <c r="R13" t="n">
-        <v>6729321</v>
+        <v>6729310</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Balningsgrop.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,44 +1928,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127303012</v>
+        <v>127302772</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>56855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,17 +1979,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478687</v>
+        <v>478700</v>
       </c>
       <c r="R14" t="n">
-        <v>6729310</v>
+        <v>6729321</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Balningsgrop.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,12 +2038,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127302711</v>
+        <v>127303229</v>
       </c>
       <c r="B29" t="n">
-        <v>91628</v>
+        <v>91557</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,26 +3493,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1101</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478561</v>
+        <v>478730</v>
       </c>
       <c r="R29" t="n">
-        <v>6729299</v>
+        <v>6729317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3564,6 +3564,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3591,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127303229</v>
+        <v>127302711</v>
       </c>
       <c r="B30" t="n">
-        <v>91557</v>
+        <v>91628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3602,26 +3607,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1101</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3637,10 +3642,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478730</v>
+        <v>478561</v>
       </c>
       <c r="R30" t="n">
-        <v>6729317</v>
+        <v>6729299</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3673,11 +3678,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4320,7 +4320,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127303026</v>
+        <v>127301945</v>
       </c>
       <c r="B37" t="n">
         <v>79020</v>
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478671</v>
+        <v>478876</v>
       </c>
       <c r="R37" t="n">
-        <v>6729323</v>
+        <v>6729339</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127301883</v>
+        <v>127303026</v>
       </c>
       <c r="B38" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478858</v>
+        <v>478671</v>
       </c>
       <c r="R38" t="n">
-        <v>6729321</v>
+        <v>6729323</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4522,51 +4522,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127301945</v>
+        <v>127303332</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478876</v>
+        <v>478721</v>
       </c>
       <c r="R39" t="n">
-        <v>6729339</v>
+        <v>6729322</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4598,81 +4603,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127303332</v>
+        <v>127301883</v>
       </c>
       <c r="B40" t="n">
-        <v>56855</v>
+        <v>78779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478721</v>
+        <v>478858</v>
       </c>
       <c r="R40" t="n">
-        <v>6729322</v>
+        <v>6729321</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4704,29 +4708,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1729,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127301869</v>
+        <v>127303012</v>
       </c>
       <c r="B12" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,26 +1740,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478861</v>
+        <v>478687</v>
       </c>
       <c r="R12" t="n">
-        <v>6729335</v>
+        <v>6729310</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1805,13 +1810,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1830,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127303012</v>
+        <v>127301869</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,31 +1850,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1873,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478687</v>
+        <v>478861</v>
       </c>
       <c r="R13" t="n">
-        <v>6729310</v>
+        <v>6729335</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1911,17 +1915,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -3073,32 +3073,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127303589</v>
+        <v>127301847</v>
       </c>
       <c r="B25" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478564</v>
+        <v>478878</v>
       </c>
       <c r="R25" t="n">
-        <v>6729339</v>
+        <v>6729286</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3147,6 +3147,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3174,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127301983</v>
+        <v>127303589</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3185,21 +3190,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3212,10 +3217,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478888</v>
+        <v>478564</v>
       </c>
       <c r="R26" t="n">
-        <v>6729340</v>
+        <v>6729339</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3275,32 +3280,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127301847</v>
+        <v>127301983</v>
       </c>
       <c r="B27" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478878</v>
+        <v>478888</v>
       </c>
       <c r="R27" t="n">
-        <v>6729286</v>
+        <v>6729340</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3349,11 +3354,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3705,32 +3705,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303130</v>
+        <v>127303176</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>91297</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,17 +3739,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478716</v>
+        <v>478757</v>
       </c>
       <c r="R31" t="n">
-        <v>6729322</v>
+        <v>6729316</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3794,19 +3794,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303112</v>
+        <v>127303130</v>
       </c>
       <c r="B32" t="n">
         <v>79020</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478674</v>
+        <v>478716</v>
       </c>
       <c r="R32" t="n">
-        <v>6729351</v>
+        <v>6729322</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303176</v>
+        <v>127303112</v>
       </c>
       <c r="B33" t="n">
-        <v>91297</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478757</v>
+        <v>478674</v>
       </c>
       <c r="R33" t="n">
-        <v>6729316</v>
+        <v>6729351</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1729,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303012</v>
+        <v>127301869</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,31 +1740,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478687</v>
+        <v>478861</v>
       </c>
       <c r="R12" t="n">
-        <v>6729310</v>
+        <v>6729335</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1810,17 +1805,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1839,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127301869</v>
+        <v>127303012</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,26 +1841,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1877,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478861</v>
+        <v>478687</v>
       </c>
       <c r="R13" t="n">
-        <v>6729335</v>
+        <v>6729310</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1915,13 +1911,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2050,51 +2050,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302578</v>
+        <v>127303145</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>56855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478547</v>
+        <v>478716</v>
       </c>
       <c r="R15" t="n">
-        <v>6729287</v>
+        <v>6729321</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2126,81 +2131,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303015</v>
+        <v>127303255</v>
       </c>
       <c r="B16" t="n">
-        <v>79638</v>
+        <v>56855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478546</v>
+        <v>478825</v>
       </c>
       <c r="R16" t="n">
-        <v>6729279</v>
+        <v>6729292</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2238,29 +2242,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303352</v>
+        <v>127302578</v>
       </c>
       <c r="B17" t="n">
-        <v>79638</v>
+        <v>80123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478560</v>
+        <v>478547</v>
       </c>
       <c r="R17" t="n">
-        <v>6729336</v>
+        <v>6729287</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2334,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2358,56 +2366,51 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303145</v>
+        <v>127303015</v>
       </c>
       <c r="B18" t="n">
-        <v>56855</v>
+        <v>79638</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478716</v>
+        <v>478546</v>
       </c>
       <c r="R18" t="n">
-        <v>6729321</v>
+        <v>6729279</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2445,74 +2448,70 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303255</v>
+        <v>127303352</v>
       </c>
       <c r="B19" t="n">
-        <v>56855</v>
+        <v>79638</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478825</v>
+        <v>478560</v>
       </c>
       <c r="R19" t="n">
-        <v>6729292</v>
+        <v>6729336</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2550,18 +2549,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4522,56 +4522,51 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127303332</v>
+        <v>127301883</v>
       </c>
       <c r="B39" t="n">
-        <v>56855</v>
+        <v>78779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478721</v>
+        <v>478858</v>
       </c>
       <c r="R39" t="n">
-        <v>6729322</v>
+        <v>6729321</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4603,80 +4598,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127301883</v>
+        <v>127303332</v>
       </c>
       <c r="B40" t="n">
-        <v>78779</v>
+        <v>56855</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478858</v>
+        <v>478721</v>
       </c>
       <c r="R40" t="n">
-        <v>6729321</v>
+        <v>6729322</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4708,25 +4704,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303347</v>
+        <v>127303609</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>80083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478585</v>
+        <v>478556</v>
       </c>
       <c r="R8" t="n">
-        <v>6729325</v>
+        <v>6729264</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,6 +1385,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,44 +1405,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302735</v>
+        <v>127303347</v>
       </c>
       <c r="B9" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,17 +1451,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478556</v>
+        <v>478585</v>
       </c>
       <c r="R9" t="n">
-        <v>6729264</v>
+        <v>6729325</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,11 +1491,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,22 +1506,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127303609</v>
+        <v>127302735</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>80152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127301821</v>
+        <v>127301869</v>
       </c>
       <c r="B11" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,28 +1635,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478847</v>
+        <v>478861</v>
       </c>
       <c r="R11" t="n">
-        <v>6729219</v>
+        <v>6729335</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1729,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127301869</v>
+        <v>127303012</v>
       </c>
       <c r="B12" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,26 +1736,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1767,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478861</v>
+        <v>478687</v>
       </c>
       <c r="R12" t="n">
-        <v>6729335</v>
+        <v>6729310</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1805,13 +1806,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1830,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127303012</v>
+        <v>127301821</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>91358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,31 +1846,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1873,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478687</v>
+        <v>478847</v>
       </c>
       <c r="R13" t="n">
-        <v>6729310</v>
+        <v>6729219</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1911,17 +1915,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2050,56 +2050,51 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127303145</v>
+        <v>127302578</v>
       </c>
       <c r="B15" t="n">
-        <v>56855</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478716</v>
+        <v>478547</v>
       </c>
       <c r="R15" t="n">
-        <v>6729321</v>
+        <v>6729287</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2131,80 +2126,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303255</v>
+        <v>127303015</v>
       </c>
       <c r="B16" t="n">
-        <v>56855</v>
+        <v>79638</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478825</v>
+        <v>478546</v>
       </c>
       <c r="R16" t="n">
-        <v>6729292</v>
+        <v>6729279</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2242,28 +2238,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127302578</v>
+        <v>127303352</v>
       </c>
       <c r="B17" t="n">
-        <v>80123</v>
+        <v>79638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,21 +2268,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2298,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478547</v>
+        <v>478560</v>
       </c>
       <c r="R17" t="n">
-        <v>6729287</v>
+        <v>6729336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2334,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,51 +2358,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303015</v>
+        <v>127303145</v>
       </c>
       <c r="B18" t="n">
-        <v>79638</v>
+        <v>56855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478546</v>
+        <v>478716</v>
       </c>
       <c r="R18" t="n">
-        <v>6729279</v>
+        <v>6729321</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2448,70 +2445,74 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303352</v>
+        <v>127303255</v>
       </c>
       <c r="B19" t="n">
-        <v>79638</v>
+        <v>56855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478560</v>
+        <v>478825</v>
       </c>
       <c r="R19" t="n">
-        <v>6729336</v>
+        <v>6729292</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,19 +2550,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3073,32 +3073,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127301847</v>
+        <v>127303589</v>
       </c>
       <c r="B25" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478878</v>
+        <v>478564</v>
       </c>
       <c r="R25" t="n">
-        <v>6729286</v>
+        <v>6729339</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3147,11 +3147,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3179,10 +3174,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127303589</v>
+        <v>127301983</v>
       </c>
       <c r="B26" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,21 +3185,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3217,10 +3212,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478564</v>
+        <v>478888</v>
       </c>
       <c r="R26" t="n">
-        <v>6729339</v>
+        <v>6729340</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3280,32 +3275,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127301983</v>
+        <v>127301847</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478888</v>
+        <v>478878</v>
       </c>
       <c r="R27" t="n">
-        <v>6729340</v>
+        <v>6729286</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3354,6 +3349,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,7 +3485,7 @@
         <v>127303229</v>
       </c>
       <c r="B29" t="n">
-        <v>91557</v>
+        <v>91563</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>127302711</v>
       </c>
       <c r="B30" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303176</v>
+        <v>127303130</v>
       </c>
       <c r="B31" t="n">
-        <v>91297</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,17 +3739,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478757</v>
+        <v>478716</v>
       </c>
       <c r="R31" t="n">
-        <v>6729316</v>
+        <v>6729322</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3794,19 +3794,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303130</v>
+        <v>127303112</v>
       </c>
       <c r="B32" t="n">
         <v>79020</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478716</v>
+        <v>478674</v>
       </c>
       <c r="R32" t="n">
-        <v>6729322</v>
+        <v>6729351</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303112</v>
+        <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>91303</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478674</v>
+        <v>478757</v>
       </c>
       <c r="R33" t="n">
-        <v>6729351</v>
+        <v>6729316</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4217,7 +4217,7 @@
         <v>127303095</v>
       </c>
       <c r="B36" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4522,51 +4522,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127301883</v>
+        <v>127303332</v>
       </c>
       <c r="B39" t="n">
-        <v>78779</v>
+        <v>56855</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478858</v>
+        <v>478721</v>
       </c>
       <c r="R39" t="n">
-        <v>6729321</v>
+        <v>6729322</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4598,81 +4603,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127303332</v>
+        <v>127301883</v>
       </c>
       <c r="B40" t="n">
-        <v>56855</v>
+        <v>78779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478721</v>
+        <v>478858</v>
       </c>
       <c r="R40" t="n">
-        <v>6729322</v>
+        <v>6729321</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4704,29 +4708,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>127303153</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>127303172</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>127303371</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127303322</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303609</v>
+        <v>127302735</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>80155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,7 +1420,7 @@
         <v>127303347</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127302735</v>
+        <v>127303609</v>
       </c>
       <c r="B10" t="n">
-        <v>80152</v>
+        <v>80086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,7 +1627,7 @@
         <v>127301869</v>
       </c>
       <c r="B11" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,32 +1725,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303012</v>
+        <v>127302772</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>56858</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,17 +1764,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478687</v>
+        <v>478700</v>
       </c>
       <c r="R12" t="n">
-        <v>6729310</v>
+        <v>6729321</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Balningsgrop.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,22 +1823,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127301821</v>
+        <v>127303012</v>
       </c>
       <c r="B13" t="n">
-        <v>91358</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,30 +1846,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1877,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478847</v>
+        <v>478687</v>
       </c>
       <c r="R13" t="n">
-        <v>6729219</v>
+        <v>6729310</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1915,13 +1916,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1940,56 +1945,55 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127302772</v>
+        <v>127301821</v>
       </c>
       <c r="B14" t="n">
-        <v>56855</v>
+        <v>91361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478700</v>
+        <v>478847</v>
       </c>
       <c r="R14" t="n">
-        <v>6729321</v>
+        <v>6729219</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,80 +2025,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302578</v>
+        <v>127303145</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>56858</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478547</v>
+        <v>478716</v>
       </c>
       <c r="R15" t="n">
-        <v>6729287</v>
+        <v>6729321</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2126,40 +2131,34 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303015</v>
+        <v>127302578</v>
       </c>
       <c r="B16" t="n">
-        <v>79638</v>
+        <v>80126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,21 +2166,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478546</v>
+        <v>478547</v>
       </c>
       <c r="R16" t="n">
-        <v>6729279</v>
+        <v>6729287</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,6 +2229,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2257,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303352</v>
+        <v>127303015</v>
       </c>
       <c r="B17" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478560</v>
+        <v>478546</v>
       </c>
       <c r="R17" t="n">
-        <v>6729336</v>
+        <v>6729279</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,56 +2362,51 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303145</v>
+        <v>127303352</v>
       </c>
       <c r="B18" t="n">
-        <v>56855</v>
+        <v>79641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478716</v>
+        <v>478560</v>
       </c>
       <c r="R18" t="n">
-        <v>6729321</v>
+        <v>6729336</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2445,18 +2444,19 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2466,7 +2466,7 @@
         <v>127303255</v>
       </c>
       <c r="B19" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>127302682</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79047</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>127303338</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>127303304</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>127302613</v>
       </c>
       <c r="B23" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>127303614</v>
       </c>
       <c r="B24" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>127303589</v>
       </c>
       <c r="B25" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>127301983</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>127301847</v>
       </c>
       <c r="B27" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>127303069</v>
       </c>
       <c r="B28" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127303229</v>
+        <v>127302711</v>
       </c>
       <c r="B29" t="n">
-        <v>91563</v>
+        <v>91637</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,26 +3493,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1101</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478730</v>
+        <v>478561</v>
       </c>
       <c r="R29" t="n">
-        <v>6729317</v>
+        <v>6729299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3564,11 +3564,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3591,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127302711</v>
+        <v>127303229</v>
       </c>
       <c r="B30" t="n">
-        <v>91634</v>
+        <v>91566</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,26 +3602,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1101</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3642,10 +3637,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478561</v>
+        <v>478730</v>
       </c>
       <c r="R30" t="n">
-        <v>6729299</v>
+        <v>6729317</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,6 +3673,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3708,7 +3708,7 @@
         <v>127303130</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>127303112</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>127303189</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>127303500</v>
       </c>
       <c r="B35" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>127303095</v>
       </c>
       <c r="B36" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>127301945</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>127303026</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>127303332</v>
       </c>
       <c r="B39" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>127301883</v>
       </c>
       <c r="B40" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>127303153</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>127303172</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>127303371</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127303322</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127302735</v>
+        <v>127303347</v>
       </c>
       <c r="B8" t="n">
-        <v>80155</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478556</v>
+        <v>478585</v>
       </c>
       <c r="R8" t="n">
-        <v>6729264</v>
+        <v>6729325</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,11 +1385,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,44 +1400,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303347</v>
+        <v>127302735</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>80161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,17 +1446,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478585</v>
+        <v>478556</v>
       </c>
       <c r="R9" t="n">
-        <v>6729325</v>
+        <v>6729264</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,6 +1486,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,12 +1506,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1521,7 +1521,7 @@
         <v>127303609</v>
       </c>
       <c r="B10" t="n">
-        <v>80086</v>
+        <v>80092</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127301869</v>
+        <v>127301821</v>
       </c>
       <c r="B11" t="n">
-        <v>79641</v>
+        <v>91369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,24 +1635,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1662,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478861</v>
+        <v>478847</v>
       </c>
       <c r="R11" t="n">
-        <v>6729335</v>
+        <v>6729219</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1725,56 +1729,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127302772</v>
+        <v>127301869</v>
       </c>
       <c r="B12" t="n">
-        <v>56858</v>
+        <v>79647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478700</v>
+        <v>478861</v>
       </c>
       <c r="R12" t="n">
-        <v>6729321</v>
+        <v>6729335</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,29 +1805,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1838,7 +1833,7 @@
         <v>127303012</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,55 +1940,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127301821</v>
+        <v>127302772</v>
       </c>
       <c r="B14" t="n">
-        <v>91361</v>
+        <v>56864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478847</v>
+        <v>478700</v>
       </c>
       <c r="R14" t="n">
-        <v>6729219</v>
+        <v>6729321</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2025,81 +2021,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127303145</v>
+        <v>127302578</v>
       </c>
       <c r="B15" t="n">
-        <v>56858</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478716</v>
+        <v>478547</v>
       </c>
       <c r="R15" t="n">
-        <v>6729321</v>
+        <v>6729287</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2131,75 +2126,86 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127302578</v>
+        <v>127303145</v>
       </c>
       <c r="B16" t="n">
-        <v>80126</v>
+        <v>56864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478547</v>
+        <v>478716</v>
       </c>
       <c r="R16" t="n">
-        <v>6729287</v>
+        <v>6729321</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,81 +2237,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303015</v>
+        <v>127303255</v>
       </c>
       <c r="B17" t="n">
-        <v>79641</v>
+        <v>56864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478546</v>
+        <v>478825</v>
       </c>
       <c r="R17" t="n">
-        <v>6729279</v>
+        <v>6729292</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2343,29 +2348,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303352</v>
+        <v>127303015</v>
       </c>
       <c r="B18" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478560</v>
+        <v>478546</v>
       </c>
       <c r="R18" t="n">
-        <v>6729336</v>
+        <v>6729279</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,56 +2467,51 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303255</v>
+        <v>127303352</v>
       </c>
       <c r="B19" t="n">
-        <v>56858</v>
+        <v>79647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478825</v>
+        <v>478560</v>
       </c>
       <c r="R19" t="n">
-        <v>6729292</v>
+        <v>6729336</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2550,18 +2549,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
         <v>127302682</v>
       </c>
       <c r="B20" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>127303338</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>127303304</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>127302613</v>
       </c>
       <c r="B23" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>127303614</v>
       </c>
       <c r="B24" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>127303589</v>
       </c>
       <c r="B25" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>127301983</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>127301847</v>
       </c>
       <c r="B27" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>127303069</v>
       </c>
       <c r="B28" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127302711</v>
+        <v>127303229</v>
       </c>
       <c r="B29" t="n">
-        <v>91637</v>
+        <v>91574</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,26 +3493,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1101</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478561</v>
+        <v>478730</v>
       </c>
       <c r="R29" t="n">
-        <v>6729299</v>
+        <v>6729317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3564,6 +3564,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3591,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127303229</v>
+        <v>127302711</v>
       </c>
       <c r="B30" t="n">
-        <v>91566</v>
+        <v>91645</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3602,26 +3607,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1101</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3637,10 +3642,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478730</v>
+        <v>478561</v>
       </c>
       <c r="R30" t="n">
-        <v>6729317</v>
+        <v>6729299</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3673,11 +3678,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303130</v>
+        <v>127303112</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478716</v>
+        <v>478674</v>
       </c>
       <c r="R31" t="n">
-        <v>6729322</v>
+        <v>6729351</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,32 +3806,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303112</v>
+        <v>127303176</v>
       </c>
       <c r="B32" t="n">
-        <v>79023</v>
+        <v>91314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3840,17 +3840,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478674</v>
+        <v>478757</v>
       </c>
       <c r="R32" t="n">
-        <v>6729351</v>
+        <v>6729316</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3895,44 +3895,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303176</v>
+        <v>127303130</v>
       </c>
       <c r="B33" t="n">
-        <v>91306</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478757</v>
+        <v>478716</v>
       </c>
       <c r="R33" t="n">
-        <v>6729316</v>
+        <v>6729322</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
         <v>127303189</v>
       </c>
       <c r="B34" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>127303500</v>
       </c>
       <c r="B35" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>127303095</v>
       </c>
       <c r="B36" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4320,10 +4320,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127301945</v>
+        <v>127303026</v>
       </c>
       <c r="B37" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478876</v>
+        <v>478671</v>
       </c>
       <c r="R37" t="n">
-        <v>6729339</v>
+        <v>6729323</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127303026</v>
+        <v>127301945</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478671</v>
+        <v>478876</v>
       </c>
       <c r="R38" t="n">
-        <v>6729323</v>
+        <v>6729339</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4525,7 +4525,7 @@
         <v>127303332</v>
       </c>
       <c r="B39" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>127301883</v>
       </c>
       <c r="B40" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127301821</v>
+        <v>127303012</v>
       </c>
       <c r="B11" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,30 +1635,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1666,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478847</v>
+        <v>478687</v>
       </c>
       <c r="R11" t="n">
-        <v>6729219</v>
+        <v>6729310</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1704,13 +1705,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1729,51 +1734,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127301869</v>
+        <v>127302772</v>
       </c>
       <c r="B12" t="n">
-        <v>79647</v>
+        <v>56864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478861</v>
+        <v>478700</v>
       </c>
       <c r="R12" t="n">
-        <v>6729335</v>
+        <v>6729321</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1805,35 +1815,39 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127303012</v>
+        <v>127301821</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,31 +1855,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1873,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478687</v>
+        <v>478847</v>
       </c>
       <c r="R13" t="n">
-        <v>6729310</v>
+        <v>6729219</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1911,17 +1924,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1940,56 +1949,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127302772</v>
+        <v>127301869</v>
       </c>
       <c r="B14" t="n">
-        <v>56864</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478700</v>
+        <v>478861</v>
       </c>
       <c r="R14" t="n">
-        <v>6729321</v>
+        <v>6729335</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,39 +2025,35 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302578</v>
+        <v>127303352</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478547</v>
+        <v>478560</v>
       </c>
       <c r="R15" t="n">
-        <v>6729287</v>
+        <v>6729336</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,11 +2124,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2366,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303015</v>
+        <v>127302578</v>
       </c>
       <c r="B18" t="n">
-        <v>79647</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,21 +2372,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2404,10 +2399,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478546</v>
+        <v>478547</v>
       </c>
       <c r="R18" t="n">
-        <v>6729279</v>
+        <v>6729287</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,6 +2435,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2467,7 +2467,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303352</v>
+        <v>127303015</v>
       </c>
       <c r="B19" t="n">
         <v>79647</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478560</v>
+        <v>478546</v>
       </c>
       <c r="R19" t="n">
-        <v>6729336</v>
+        <v>6729279</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2770,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127303304</v>
+        <v>127302613</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,21 +2781,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2804,17 +2804,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478650</v>
+        <v>478547</v>
       </c>
       <c r="R22" t="n">
-        <v>6729332</v>
+        <v>6729247</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2859,19 +2859,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302613</v>
+        <v>127303614</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -2905,17 +2905,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478547</v>
+        <v>478567</v>
       </c>
       <c r="R23" t="n">
-        <v>6729247</v>
+        <v>6729335</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2960,22 +2960,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127303614</v>
+        <v>127303304</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,21 +2983,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478567</v>
+        <v>478650</v>
       </c>
       <c r="R24" t="n">
-        <v>6729335</v>
+        <v>6729332</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3073,32 +3073,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127303589</v>
+        <v>127301847</v>
       </c>
       <c r="B25" t="n">
-        <v>79647</v>
+        <v>92640</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478564</v>
+        <v>478878</v>
       </c>
       <c r="R25" t="n">
-        <v>6729339</v>
+        <v>6729286</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3147,6 +3147,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3275,32 +3280,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127301847</v>
+        <v>127303589</v>
       </c>
       <c r="B27" t="n">
-        <v>92639</v>
+        <v>79647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478878</v>
+        <v>478564</v>
       </c>
       <c r="R27" t="n">
-        <v>6729286</v>
+        <v>6729339</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3349,11 +3354,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,7 +3485,7 @@
         <v>127303229</v>
       </c>
       <c r="B29" t="n">
-        <v>91574</v>
+        <v>91575</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>127302711</v>
       </c>
       <c r="B30" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303112</v>
+        <v>127303130</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478674</v>
+        <v>478716</v>
       </c>
       <c r="R31" t="n">
-        <v>6729351</v>
+        <v>6729322</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,32 +3806,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303176</v>
+        <v>127303112</v>
       </c>
       <c r="B32" t="n">
-        <v>91314</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3840,17 +3840,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478757</v>
+        <v>478674</v>
       </c>
       <c r="R32" t="n">
-        <v>6729316</v>
+        <v>6729351</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3895,44 +3895,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303130</v>
+        <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>91315</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478716</v>
+        <v>478757</v>
       </c>
       <c r="R33" t="n">
-        <v>6729322</v>
+        <v>6729316</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4217,7 +4217,7 @@
         <v>127303095</v>
       </c>
       <c r="B36" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127303026</v>
+        <v>127301945</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478671</v>
+        <v>478876</v>
       </c>
       <c r="R37" t="n">
-        <v>6729323</v>
+        <v>6729339</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127301945</v>
+        <v>127303026</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478876</v>
+        <v>478671</v>
       </c>
       <c r="R38" t="n">
-        <v>6729339</v>
+        <v>6729323</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303347</v>
+        <v>127303609</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>80092</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478585</v>
+        <v>478556</v>
       </c>
       <c r="R8" t="n">
-        <v>6729325</v>
+        <v>6729264</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,6 +1385,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,44 +1405,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302735</v>
+        <v>127303347</v>
       </c>
       <c r="B9" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,17 +1451,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478556</v>
+        <v>478585</v>
       </c>
       <c r="R9" t="n">
-        <v>6729264</v>
+        <v>6729325</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,11 +1491,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,22 +1506,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127303609</v>
+        <v>127302735</v>
       </c>
       <c r="B10" t="n">
-        <v>80092</v>
+        <v>80161</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303012</v>
+        <v>127301869</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,31 +1635,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478687</v>
+        <v>478861</v>
       </c>
       <c r="R11" t="n">
-        <v>6729310</v>
+        <v>6729335</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1705,17 +1700,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1734,32 +1725,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127302772</v>
+        <v>127303012</v>
       </c>
       <c r="B12" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,17 +1764,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478700</v>
+        <v>478687</v>
       </c>
       <c r="R12" t="n">
-        <v>6729321</v>
+        <v>6729310</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1817,7 +1808,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Balningsgrop.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,12 +1823,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1949,51 +1940,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127301869</v>
+        <v>127302772</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>56864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478861</v>
+        <v>478700</v>
       </c>
       <c r="R14" t="n">
-        <v>6729335</v>
+        <v>6729321</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2025,35 +2021,39 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127303352</v>
+        <v>127302578</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478560</v>
+        <v>478547</v>
       </c>
       <c r="R15" t="n">
-        <v>6729336</v>
+        <v>6729287</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,6 +2124,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,56 +2156,51 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303145</v>
+        <v>127303015</v>
       </c>
       <c r="B16" t="n">
-        <v>56864</v>
+        <v>79647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478716</v>
+        <v>478546</v>
       </c>
       <c r="R16" t="n">
-        <v>6729321</v>
+        <v>6729279</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2238,74 +2238,70 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303255</v>
+        <v>127303352</v>
       </c>
       <c r="B17" t="n">
-        <v>56864</v>
+        <v>79647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478825</v>
+        <v>478560</v>
       </c>
       <c r="R17" t="n">
-        <v>6729292</v>
+        <v>6729336</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2343,69 +2339,75 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127302578</v>
+        <v>127303145</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>56864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478547</v>
+        <v>478716</v>
       </c>
       <c r="R18" t="n">
-        <v>6729287</v>
+        <v>6729321</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2437,81 +2439,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303015</v>
+        <v>127303255</v>
       </c>
       <c r="B19" t="n">
-        <v>79647</v>
+        <v>56864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478546</v>
+        <v>478825</v>
       </c>
       <c r="R19" t="n">
-        <v>6729279</v>
+        <v>6729292</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,19 +2550,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127302613</v>
+        <v>127303614</v>
       </c>
       <c r="B22" t="n">
         <v>78788</v>
@@ -2804,17 +2804,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478547</v>
+        <v>478567</v>
       </c>
       <c r="R22" t="n">
-        <v>6729247</v>
+        <v>6729335</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2859,22 +2859,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127303614</v>
+        <v>127303304</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,21 +2882,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478567</v>
+        <v>478650</v>
       </c>
       <c r="R23" t="n">
-        <v>6729335</v>
+        <v>6729332</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127303304</v>
+        <v>127302613</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,21 +2983,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3006,17 +3006,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478650</v>
+        <v>478547</v>
       </c>
       <c r="R24" t="n">
-        <v>6729332</v>
+        <v>6729247</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3061,12 +3061,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127301983</v>
+        <v>127303589</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,21 +3190,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478888</v>
+        <v>478564</v>
       </c>
       <c r="R26" t="n">
-        <v>6729340</v>
+        <v>6729339</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3280,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127303589</v>
+        <v>127301983</v>
       </c>
       <c r="B27" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,21 +3291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478564</v>
+        <v>478888</v>
       </c>
       <c r="R27" t="n">
-        <v>6729339</v>
+        <v>6729340</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303130</v>
+        <v>127303176</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>91315</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,17 +3739,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478716</v>
+        <v>478757</v>
       </c>
       <c r="R31" t="n">
-        <v>6729322</v>
+        <v>6729316</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3794,19 +3794,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303112</v>
+        <v>127303130</v>
       </c>
       <c r="B32" t="n">
         <v>79029</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478674</v>
+        <v>478716</v>
       </c>
       <c r="R32" t="n">
-        <v>6729351</v>
+        <v>6729322</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303176</v>
+        <v>127303112</v>
       </c>
       <c r="B33" t="n">
-        <v>91315</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478757</v>
+        <v>478674</v>
       </c>
       <c r="R33" t="n">
-        <v>6729316</v>
+        <v>6729351</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4320,51 +4320,56 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127301945</v>
+        <v>127303332</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478876</v>
+        <v>478721</v>
       </c>
       <c r="R37" t="n">
-        <v>6729339</v>
+        <v>6729322</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4396,35 +4401,39 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127303026</v>
+        <v>127301883</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4432,21 +4441,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4459,10 +4468,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478671</v>
+        <v>478858</v>
       </c>
       <c r="R38" t="n">
-        <v>6729323</v>
+        <v>6729321</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4522,56 +4531,51 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127303332</v>
+        <v>127301945</v>
       </c>
       <c r="B39" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478721</v>
+        <v>478876</v>
       </c>
       <c r="R39" t="n">
-        <v>6729322</v>
+        <v>6729339</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4603,39 +4607,35 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127301883</v>
+        <v>127303026</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4670,10 +4670,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478858</v>
+        <v>478671</v>
       </c>
       <c r="R40" t="n">
-        <v>6729321</v>
+        <v>6729323</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -1624,51 +1624,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127301869</v>
+        <v>127302772</v>
       </c>
       <c r="B11" t="n">
-        <v>79647</v>
+        <v>56864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478861</v>
+        <v>478700</v>
       </c>
       <c r="R11" t="n">
-        <v>6729335</v>
+        <v>6729321</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,25 +1705,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1838,7 +1847,7 @@
         <v>127301821</v>
       </c>
       <c r="B13" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,56 +1949,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127302772</v>
+        <v>127301869</v>
       </c>
       <c r="B14" t="n">
-        <v>56864</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478700</v>
+        <v>478861</v>
       </c>
       <c r="R14" t="n">
-        <v>6729321</v>
+        <v>6729335</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,39 +2025,35 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302578</v>
+        <v>127303015</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478547</v>
+        <v>478546</v>
       </c>
       <c r="R15" t="n">
-        <v>6729287</v>
+        <v>6729279</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,11 +2124,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127303015</v>
+        <v>127302578</v>
       </c>
       <c r="B16" t="n">
-        <v>79647</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,21 +2162,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478546</v>
+        <v>478547</v>
       </c>
       <c r="R16" t="n">
-        <v>6729279</v>
+        <v>6729287</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,6 +2225,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2770,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127303614</v>
+        <v>127303304</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,21 +2781,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478567</v>
+        <v>478650</v>
       </c>
       <c r="R22" t="n">
-        <v>6729335</v>
+        <v>6729332</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127303304</v>
+        <v>127302613</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,21 +2882,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2905,17 +2905,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478650</v>
+        <v>478547</v>
       </c>
       <c r="R23" t="n">
-        <v>6729332</v>
+        <v>6729247</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2960,19 +2960,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127302613</v>
+        <v>127303614</v>
       </c>
       <c r="B24" t="n">
         <v>78788</v>
@@ -3006,17 +3006,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478547</v>
+        <v>478567</v>
       </c>
       <c r="R24" t="n">
-        <v>6729247</v>
+        <v>6729335</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3061,44 +3061,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127301847</v>
+        <v>127301983</v>
       </c>
       <c r="B25" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478878</v>
+        <v>478888</v>
       </c>
       <c r="R25" t="n">
-        <v>6729286</v>
+        <v>6729340</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3147,11 +3147,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3179,32 +3174,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127303589</v>
+        <v>127301847</v>
       </c>
       <c r="B26" t="n">
-        <v>79647</v>
+        <v>92641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3217,10 +3212,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478564</v>
+        <v>478878</v>
       </c>
       <c r="R26" t="n">
-        <v>6729339</v>
+        <v>6729286</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3253,6 +3248,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127301983</v>
+        <v>127303589</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,21 +3291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478888</v>
+        <v>478564</v>
       </c>
       <c r="R27" t="n">
-        <v>6729340</v>
+        <v>6729339</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3485,7 +3485,7 @@
         <v>127303229</v>
       </c>
       <c r="B29" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>127302711</v>
       </c>
       <c r="B30" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303176</v>
+        <v>127303130</v>
       </c>
       <c r="B31" t="n">
-        <v>91315</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,17 +3739,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478757</v>
+        <v>478716</v>
       </c>
       <c r="R31" t="n">
-        <v>6729316</v>
+        <v>6729322</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3794,19 +3794,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303130</v>
+        <v>127303112</v>
       </c>
       <c r="B32" t="n">
         <v>79029</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478716</v>
+        <v>478674</v>
       </c>
       <c r="R32" t="n">
-        <v>6729322</v>
+        <v>6729351</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303112</v>
+        <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>91316</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,17 +3941,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478674</v>
+        <v>478757</v>
       </c>
       <c r="R33" t="n">
-        <v>6729351</v>
+        <v>6729316</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4217,7 +4217,7 @@
         <v>127303095</v>
       </c>
       <c r="B36" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4320,56 +4320,51 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127303332</v>
+        <v>127301945</v>
       </c>
       <c r="B37" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478721</v>
+        <v>478876</v>
       </c>
       <c r="R37" t="n">
-        <v>6729322</v>
+        <v>6729339</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4401,39 +4396,35 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127301883</v>
+        <v>127303026</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4441,21 +4432,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4468,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478858</v>
+        <v>478671</v>
       </c>
       <c r="R38" t="n">
-        <v>6729321</v>
+        <v>6729323</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4531,51 +4522,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127301945</v>
+        <v>127303332</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478876</v>
+        <v>478721</v>
       </c>
       <c r="R39" t="n">
-        <v>6729339</v>
+        <v>6729322</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4607,35 +4603,39 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127303026</v>
+        <v>127301883</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4670,10 +4670,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478671</v>
+        <v>478858</v>
       </c>
       <c r="R40" t="n">
-        <v>6729323</v>
+        <v>6729321</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126844779</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126844784</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>127303153</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>127303172</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>127303371</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127303322</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127303609</v>
       </c>
       <c r="B8" t="n">
-        <v>80092</v>
+        <v>80074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>127303347</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>127302735</v>
       </c>
       <c r="B10" t="n">
-        <v>80161</v>
+        <v>80143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,56 +1624,55 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127302772</v>
+        <v>127301821</v>
       </c>
       <c r="B11" t="n">
-        <v>56864</v>
+        <v>91339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478700</v>
+        <v>478847</v>
       </c>
       <c r="R11" t="n">
-        <v>6729321</v>
+        <v>6729219</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,39 +1704,35 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303012</v>
+        <v>127301869</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,31 +1740,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1777,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478687</v>
+        <v>478861</v>
       </c>
       <c r="R12" t="n">
-        <v>6729310</v>
+        <v>6729335</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1815,17 +1805,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1844,55 +1830,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127301821</v>
+        <v>127302772</v>
       </c>
       <c r="B13" t="n">
-        <v>91371</v>
+        <v>56849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478847</v>
+        <v>478700</v>
       </c>
       <c r="R13" t="n">
-        <v>6729219</v>
+        <v>6729321</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1924,35 +1911,39 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127301869</v>
+        <v>127303012</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,26 +1951,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1987,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478861</v>
+        <v>478687</v>
       </c>
       <c r="R14" t="n">
-        <v>6729335</v>
+        <v>6729310</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2025,13 +2021,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127303015</v>
+        <v>127302578</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478546</v>
+        <v>478547</v>
       </c>
       <c r="R15" t="n">
-        <v>6729279</v>
+        <v>6729287</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,6 +2124,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,51 +2156,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127302578</v>
+        <v>127303145</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>56849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478547</v>
+        <v>478716</v>
       </c>
       <c r="R16" t="n">
-        <v>6729287</v>
+        <v>6729321</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2227,81 +2237,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303352</v>
+        <v>127303255</v>
       </c>
       <c r="B17" t="n">
-        <v>79647</v>
+        <v>56849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478560</v>
+        <v>478825</v>
       </c>
       <c r="R17" t="n">
-        <v>6729336</v>
+        <v>6729292</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2339,75 +2348,69 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303145</v>
+        <v>127303015</v>
       </c>
       <c r="B18" t="n">
-        <v>56864</v>
+        <v>79629</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478716</v>
+        <v>478546</v>
       </c>
       <c r="R18" t="n">
-        <v>6729321</v>
+        <v>6729279</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2445,74 +2448,70 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303255</v>
+        <v>127303352</v>
       </c>
       <c r="B19" t="n">
-        <v>56864</v>
+        <v>79629</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478825</v>
+        <v>478560</v>
       </c>
       <c r="R19" t="n">
-        <v>6729292</v>
+        <v>6729336</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2550,18 +2549,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
         <v>127302682</v>
       </c>
       <c r="B20" t="n">
-        <v>79053</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>127303338</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>127303304</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>127302613</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>127303614</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>127301983</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>127301847</v>
       </c>
       <c r="B26" t="n">
-        <v>92641</v>
+        <v>92609</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>127303589</v>
       </c>
       <c r="B27" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>127303069</v>
       </c>
       <c r="B28" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>127303229</v>
       </c>
       <c r="B29" t="n">
-        <v>91576</v>
+        <v>91544</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>127302711</v>
       </c>
       <c r="B30" t="n">
-        <v>91647</v>
+        <v>91615</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>127303130</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>127303112</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>127303176</v>
       </c>
       <c r="B33" t="n">
-        <v>91316</v>
+        <v>91284</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>127303189</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>127303500</v>
       </c>
       <c r="B35" t="n">
-        <v>56864</v>
+        <v>56849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>127303095</v>
       </c>
       <c r="B36" t="n">
-        <v>92641</v>
+        <v>92609</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>127301945</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127303026</v>
+        <v>127301883</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>78770</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478671</v>
+        <v>478858</v>
       </c>
       <c r="R38" t="n">
-        <v>6729323</v>
+        <v>6729321</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4522,56 +4522,51 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127303332</v>
+        <v>127303026</v>
       </c>
       <c r="B39" t="n">
-        <v>56864</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478721</v>
+        <v>478671</v>
       </c>
       <c r="R39" t="n">
-        <v>6729322</v>
+        <v>6729323</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4603,80 +4598,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127301883</v>
+        <v>127303332</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>56849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478858</v>
+        <v>478721</v>
       </c>
       <c r="R40" t="n">
-        <v>6729321</v>
+        <v>6729322</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4708,25 +4704,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126844779</v>
+        <v>127302711</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>478561</v>
       </c>
       <c r="R2" t="n">
-        <v>6729257</v>
+        <v>6729299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,65 +772,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126844784</v>
+        <v>127303229</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>92147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478556</v>
+        <v>478730</v>
       </c>
       <c r="R3" t="n">
-        <v>6729266</v>
+        <v>6729317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,22 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På granstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,22 +886,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127303153</v>
+        <v>127301847</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,17 +932,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478581</v>
+        <v>478878</v>
       </c>
       <c r="R4" t="n">
-        <v>6729333</v>
+        <v>6729286</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,6 +972,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,22 +992,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127303172</v>
+        <v>127303095</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,17 +1038,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478612</v>
+        <v>478673</v>
       </c>
       <c r="R5" t="n">
-        <v>6729327</v>
+        <v>6729316</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,6 +1078,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,22 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127303371</v>
+        <v>127301821</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,24 +1121,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1147,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478608</v>
+        <v>478847</v>
       </c>
       <c r="R6" t="n">
-        <v>6729328</v>
+        <v>6729219</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1210,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127303322</v>
+        <v>127303176</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478641</v>
+        <v>478757</v>
       </c>
       <c r="R7" t="n">
-        <v>6729307</v>
+        <v>6729316</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,32 +1316,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303609</v>
+        <v>127301945</v>
       </c>
       <c r="B8" t="n">
-        <v>80092</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,17 +1350,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478556</v>
+        <v>478876</v>
       </c>
       <c r="R8" t="n">
-        <v>6729264</v>
+        <v>6729339</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,11 +1390,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,26 +1405,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303347</v>
+        <v>127301983</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478585</v>
+        <v>478888</v>
       </c>
       <c r="R9" t="n">
-        <v>6729325</v>
+        <v>6729340</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1518,32 +1518,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127302735</v>
+        <v>127303026</v>
       </c>
       <c r="B10" t="n">
-        <v>80161</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,17 +1552,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478556</v>
+        <v>478671</v>
       </c>
       <c r="R10" t="n">
-        <v>6729264</v>
+        <v>6729323</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1592,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,54 +1607,49 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127302772</v>
+        <v>127303112</v>
       </c>
       <c r="B11" t="n">
-        <v>56864</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1667,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478700</v>
+        <v>478674</v>
       </c>
       <c r="R11" t="n">
-        <v>6729321</v>
+        <v>6729351</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,17 +1695,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1734,56 +1720,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303012</v>
+        <v>127303130</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478687</v>
+        <v>478716</v>
       </c>
       <c r="R12" t="n">
-        <v>6729310</v>
+        <v>6729322</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,84 +1796,76 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127301821</v>
+        <v>127303153</v>
       </c>
       <c r="B13" t="n">
-        <v>91371</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478847</v>
+        <v>478581</v>
       </c>
       <c r="R13" t="n">
-        <v>6729219</v>
+        <v>6729333</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1937,44 +1910,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127301869</v>
+        <v>127303172</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,17 +1956,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478861</v>
+        <v>478612</v>
       </c>
       <c r="R14" t="n">
-        <v>6729335</v>
+        <v>6729327</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2038,44 +2011,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127303015</v>
+        <v>127303189</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478546</v>
+        <v>478644</v>
       </c>
       <c r="R15" t="n">
-        <v>6729279</v>
+        <v>6729336</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,32 +2124,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127302578</v>
+        <v>127303304</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,17 +2158,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478547</v>
+        <v>478650</v>
       </c>
       <c r="R16" t="n">
-        <v>6729287</v>
+        <v>6729332</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2225,11 +2198,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,44 +2213,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303352</v>
+        <v>127303322</v>
       </c>
       <c r="B17" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,17 +2259,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478560</v>
+        <v>478641</v>
       </c>
       <c r="R17" t="n">
-        <v>6729336</v>
+        <v>6729307</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2346,54 +2314,49 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127303145</v>
+        <v>127303338</v>
       </c>
       <c r="B18" t="n">
-        <v>56864</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2401,10 +2364,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478716</v>
+        <v>478615</v>
       </c>
       <c r="R18" t="n">
-        <v>6729321</v>
+        <v>6729304</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2445,6 +2408,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2463,42 +2427,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127303255</v>
+        <v>127303347</v>
       </c>
       <c r="B19" t="n">
-        <v>56864</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2506,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478825</v>
+        <v>478585</v>
       </c>
       <c r="R19" t="n">
-        <v>6729292</v>
+        <v>6729325</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2550,6 +2509,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2568,32 +2528,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127302682</v>
+        <v>127303371</v>
       </c>
       <c r="B20" t="n">
-        <v>79053</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2602,17 +2562,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478682</v>
+        <v>478608</v>
       </c>
       <c r="R20" t="n">
-        <v>6729327</v>
+        <v>6729328</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2657,44 +2617,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127303338</v>
+        <v>127302682</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,17 +2663,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478615</v>
+        <v>478682</v>
       </c>
       <c r="R21" t="n">
-        <v>6729304</v>
+        <v>6729327</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2758,22 +2718,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127303304</v>
+        <v>127301869</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2808,10 +2768,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478650</v>
+        <v>478861</v>
       </c>
       <c r="R22" t="n">
-        <v>6729332</v>
+        <v>6729335</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2871,10 +2831,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302613</v>
+        <v>127303015</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2909,10 +2869,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478547</v>
+        <v>478546</v>
       </c>
       <c r="R23" t="n">
-        <v>6729247</v>
+        <v>6729279</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2972,10 +2932,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127303614</v>
+        <v>127303069</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,21 +2943,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,10 +2970,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478567</v>
+        <v>478692</v>
       </c>
       <c r="R24" t="n">
-        <v>6729335</v>
+        <v>6729327</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3073,10 +3033,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127301983</v>
+        <v>127303352</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,21 +3044,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3107,17 +3067,17 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478888</v>
+        <v>478560</v>
       </c>
       <c r="R25" t="n">
-        <v>6729340</v>
+        <v>6729336</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3162,44 +3122,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127301847</v>
+        <v>127303589</v>
       </c>
       <c r="B26" t="n">
-        <v>92641</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3212,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478878</v>
+        <v>478564</v>
       </c>
       <c r="R26" t="n">
-        <v>6729286</v>
+        <v>6729339</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3248,11 +3208,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3280,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127303589</v>
+        <v>127302578</v>
       </c>
       <c r="B27" t="n">
-        <v>79647</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,21 +3246,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3314,17 +3269,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478564</v>
+        <v>478547</v>
       </c>
       <c r="R27" t="n">
-        <v>6729339</v>
+        <v>6729287</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3354,6 +3309,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På liggande sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3369,44 +3329,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127303069</v>
+        <v>127302735</v>
       </c>
       <c r="B28" t="n">
-        <v>79647</v>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3415,17 +3375,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478692</v>
+        <v>478556</v>
       </c>
       <c r="R28" t="n">
-        <v>6729327</v>
+        <v>6729264</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3455,6 +3415,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3470,22 +3435,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127303229</v>
+        <v>127303012</v>
       </c>
       <c r="B29" t="n">
-        <v>91576</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,48 +3458,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1101</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478730</v>
+        <v>478687</v>
       </c>
       <c r="R29" t="n">
-        <v>6729317</v>
+        <v>6729310</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3568,7 +3530,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granstubbe.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3577,64 +3539,60 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127302711</v>
+        <v>127302772</v>
       </c>
       <c r="B30" t="n">
-        <v>91647</v>
+        <v>57141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3642,10 +3600,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478561</v>
+        <v>478700</v>
       </c>
       <c r="R30" t="n">
-        <v>6729299</v>
+        <v>6729321</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,13 +3638,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3705,51 +3667,56 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127303130</v>
+        <v>127303145</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>57141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
         <v>478716</v>
       </c>
       <c r="R31" t="n">
-        <v>6729322</v>
+        <v>6729321</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3787,70 +3754,74 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127303112</v>
+        <v>127303255</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>57141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478674</v>
+        <v>478825</v>
       </c>
       <c r="R32" t="n">
-        <v>6729351</v>
+        <v>6729292</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3888,29 +3859,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127303176</v>
+        <v>127303332</v>
       </c>
       <c r="B33" t="n">
-        <v>91316</v>
+        <v>57141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3918,40 +3888,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478757</v>
+        <v>478721</v>
       </c>
       <c r="R33" t="n">
-        <v>6729316</v>
+        <v>6729322</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3983,76 +3958,85 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127303189</v>
+        <v>127303500</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478644</v>
+        <v>478575</v>
       </c>
       <c r="R34" t="n">
-        <v>6729336</v>
+        <v>6729351</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4090,29 +4074,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127303500</v>
+        <v>127303938</v>
       </c>
       <c r="B35" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4152,13 +4135,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478575</v>
+        <v>478417</v>
       </c>
       <c r="R35" t="n">
-        <v>6729351</v>
+        <v>6729231</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4185,9 +4168,19 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4202,63 +4195,68 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127303095</v>
+        <v>126844779</v>
       </c>
       <c r="B36" t="n">
-        <v>92641</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478673</v>
+        <v>478561</v>
       </c>
       <c r="R36" t="n">
-        <v>6729316</v>
+        <v>6729257</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4282,17 +4280,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4308,63 +4311,68 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127301945</v>
+        <v>126844784</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478876</v>
+        <v>478556</v>
       </c>
       <c r="R37" t="n">
-        <v>6729339</v>
+        <v>6729266</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4388,12 +4396,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4409,22 +4427,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127303026</v>
+        <v>127301883</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4432,21 +4450,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4459,10 +4477,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478671</v>
+        <v>478858</v>
       </c>
       <c r="R38" t="n">
-        <v>6729323</v>
+        <v>6729321</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4522,42 +4540,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127303332</v>
+        <v>127302613</v>
       </c>
       <c r="B39" t="n">
-        <v>56864</v>
+        <v>79085</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4565,10 +4578,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478721</v>
+        <v>478547</v>
       </c>
       <c r="R39" t="n">
-        <v>6729322</v>
+        <v>6729247</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4603,17 +4616,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4632,10 +4641,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127301883</v>
+        <v>127303614</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>79085</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4670,10 +4679,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478858</v>
+        <v>478567</v>
       </c>
       <c r="R40" t="n">
-        <v>6729321</v>
+        <v>6729335</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4730,6 +4739,112 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127303609</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>478556</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6729264</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31967-2025 artfynd.xlsx
+++ b/artfynd/A 31967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302711</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303229</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127301847</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303095</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127301821</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303176</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127301945</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127301983</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303026</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303112</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1818,6 +1873,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303130</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1919,6 +1979,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303153</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2020,6 +2085,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303172</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2121,6 +2191,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303189</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2222,6 +2297,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303304</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2323,6 +2403,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303322</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2424,6 +2509,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303338</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2525,6 +2615,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303347</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2626,6 +2721,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303371</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2727,6 +2827,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302682</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2828,6 +2933,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127301869</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2929,6 +3039,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303015</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3030,6 +3145,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303069</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3131,6 +3251,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303352</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3232,6 +3357,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303589</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3338,6 +3468,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302578</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3444,6 +3579,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302735</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3554,6 +3694,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303012</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3664,6 +3809,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302772</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3769,6 +3919,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303145</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3874,6 +4029,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303255</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3984,6 +4144,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303332</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4089,6 +4254,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303500</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4204,6 +4374,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303938</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4320,6 +4495,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126844779</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4436,6 +4616,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126844784</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4537,6 +4722,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127301883</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4638,6 +4828,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302613</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4739,6 +4934,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303614</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4845,8 +5045,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303609</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>